--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634366E9-CAA4-4E71-A5B7-81BDDB9AA9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F28C50-5FA7-4C2D-9B48-FBDAAF9F33A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
   <si>
     <t>Reports Name</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>WNS Pennymac Call Volume Trend</t>
+  </si>
+  <si>
+    <t>Consolidated System Issue and No Station Tracker</t>
   </si>
 </sst>
 </file>
@@ -638,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -672,8 +675,8 @@
         <v>46001</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f>IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/10/2025</v>
+        <f>A2</f>
+        <v>WNS PennyMac Performance Trend</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -687,8 +690,8 @@
         <v>46001</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f t="shared" ref="D3:D52" si="0">IF(OR(C3="-",C3=""),"",$C$1&amp;" "&amp;TEXT(C3,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/10/2025</v>
+        <f t="shared" ref="D3:D29" si="0">A3</f>
+        <v>Performance Dashboard</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -703,7 +706,7 @@
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Productivity Dashboard</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -718,7 +721,7 @@
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>WNS PennyMac MTD Adherence Report</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -733,7 +736,7 @@
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>PennySaved Dashboard</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -748,7 +751,7 @@
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>WNS PennyMac Servicing Performance Outliers Report</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -763,7 +766,7 @@
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/03/2025</v>
+        <v>WNS Pennymac Supervisor Call Tracker</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -778,7 +781,7 @@
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/01/2025</v>
+        <v>PennyMac's Performance Review Report</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -793,7 +796,7 @@
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>WNS PennyMac Excessive Extended Wrap Report</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -808,7 +811,7 @@
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>WNS PennyMac Servicing AHT Trend</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -823,7 +826,7 @@
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>WNS Pennymac Attendance Report</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -836,7 +839,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Servicing VL Tracker</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -849,7 +852,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac LOA/Absconding Tracker</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -864,7 +867,7 @@
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac OT/RDOT Tracker</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -879,7 +882,7 @@
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Attendance &amp; PennySaved Kicker</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,7 +897,7 @@
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Tech Tardy vs Regular Tardy Report</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -909,7 +912,7 @@
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>WNS PennyMac Consolidated System Issue Report -</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -924,7 +927,7 @@
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Servicing Multiple Log-out Instance Report</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -939,7 +942,7 @@
       </c>
       <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Proper Log Off EOD Report</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +957,7 @@
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac JIRA TAR Form</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -969,7 +972,7 @@
       </c>
       <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac OJT - Pull Out Request</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -984,7 +987,7 @@
       </c>
       <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Clinic log-out Form</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -999,7 +1002,7 @@
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS Plotted Activity Tracker</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1014,7 +1017,7 @@
       </c>
       <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac DNS AM Schedule Tracker</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1029,7 +1032,7 @@
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>WNS PennyMac Servicing Scorecard</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1044,7 +1047,7 @@
       </c>
       <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac Coaching Logs</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1059,7 +1062,7 @@
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>WNS PennyMac RDOT Incentive</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1074,7 +1077,7 @@
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>WNS PennyMac SM DNP &amp; Productivity Incentive</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,7 +1091,7 @@
         <v>46001</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:D55" si="1">IF(OR(C30="-",C30=""),"",$C$1&amp;" "&amp;TEXT(C30,"mm/dd/yyyy"))</f>
         <v>Updated as of 12/10/2025</v>
       </c>
     </row>
@@ -1103,7 +1106,7 @@
         <v>46001</v>
       </c>
       <c r="D31" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 12/10/2025</v>
       </c>
     </row>
@@ -1118,7 +1121,7 @@
         <v>61</v>
       </c>
       <c r="D32" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1133,7 +1136,7 @@
         <v>61</v>
       </c>
       <c r="D33" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1148,7 +1151,7 @@
         <v>61</v>
       </c>
       <c r="D34" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1163,7 +1166,7 @@
         <v>61</v>
       </c>
       <c r="D35" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1178,7 +1181,7 @@
         <v>45982</v>
       </c>
       <c r="D36" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/21/2025</v>
       </c>
     </row>
@@ -1193,7 +1196,7 @@
         <v>45986</v>
       </c>
       <c r="D37" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/25/2025</v>
       </c>
     </row>
@@ -1208,7 +1211,7 @@
         <v>45986</v>
       </c>
       <c r="D38" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/25/2025</v>
       </c>
     </row>
@@ -1223,7 +1226,7 @@
         <v>45980</v>
       </c>
       <c r="D39" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/19/2025</v>
       </c>
     </row>
@@ -1238,7 +1241,7 @@
         <v>45987</v>
       </c>
       <c r="D40" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/26/2025</v>
       </c>
     </row>
@@ -1253,7 +1256,7 @@
         <v>45986</v>
       </c>
       <c r="D41" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/25/2025</v>
       </c>
     </row>
@@ -1268,7 +1271,7 @@
         <v>61</v>
       </c>
       <c r="D42" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1280,7 +1283,7 @@
         <v>61</v>
       </c>
       <c r="D43" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1292,7 +1295,7 @@
         <v>61</v>
       </c>
       <c r="D44" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1314,7 +1317,7 @@
         <v>45990</v>
       </c>
       <c r="D46" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/29/2025</v>
       </c>
     </row>
@@ -1329,7 +1332,7 @@
         <v>45980</v>
       </c>
       <c r="D47" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 11/19/2025</v>
       </c>
     </row>
@@ -1341,7 +1344,7 @@
         <v>61</v>
       </c>
       <c r="D48" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1356,7 +1359,7 @@
         <v>46000</v>
       </c>
       <c r="D49" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 12/09/2025</v>
       </c>
     </row>
@@ -1371,7 +1374,7 @@
         <v>46000</v>
       </c>
       <c r="D50" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 12/09/2025</v>
       </c>
     </row>
@@ -1386,7 +1389,7 @@
         <v>46000</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 12/09/2025</v>
       </c>
     </row>
@@ -1401,15 +1404,32 @@
         <v>46000</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 12/09/2025</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="C53" s="2"/>
+      <c r="D53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
+      <c r="D54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D55" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1456,8 +1476,9 @@
     <hyperlink ref="A49" r:id="rId41" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
     <hyperlink ref="A51" r:id="rId42" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
     <hyperlink ref="A52" r:id="rId43" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId44" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId45"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F28C50-5FA7-4C2D-9B48-FBDAAF9F33A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA4F91-3197-459F-91BD-891AE25F2961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -675,8 +675,8 @@
         <v>46001</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f>A2</f>
-        <v>WNS PennyMac Performance Trend</v>
+        <f t="shared" ref="D2:D55" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -690,8 +690,8 @@
         <v>46001</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f t="shared" ref="D3:D29" si="0">A3</f>
-        <v>Performance Dashboard</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -706,7 +706,7 @@
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Productivity Dashboard</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac MTD Adherence Report</v>
+        <v>Updated as of 12/09/2025</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -736,7 +736,7 @@
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>PennySaved Dashboard</v>
+        <v>Updated as of 12/08/2025</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Servicing Performance Outliers Report</v>
+        <v>Updated as of 12/08/2025</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -766,7 +766,7 @@
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS Pennymac Supervisor Call Tracker</v>
+        <v>Updated as of 12/03/2025</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -781,7 +781,7 @@
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>PennyMac's Performance Review Report</v>
+        <v>Updated as of 12/01/2025</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -796,7 +796,7 @@
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Excessive Extended Wrap Report</v>
+        <v>Updated as of 12/09/2025</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Servicing AHT Trend</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -826,7 +826,7 @@
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS Pennymac Attendance Report</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -839,7 +839,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Servicing VL Tracker</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac LOA/Absconding Tracker</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -867,7 +867,7 @@
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac OT/RDOT Tracker</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Attendance &amp; PennySaved Kicker</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -897,7 +897,7 @@
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Tech Tardy vs Regular Tardy Report</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Consolidated System Issue Report -</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -927,7 +927,7 @@
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Servicing Multiple Log-out Instance Report</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
       </c>
       <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Proper Log Off EOD Report</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -957,7 +957,7 @@
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac JIRA TAR Form</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -972,7 +972,7 @@
       </c>
       <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac OJT - Pull Out Request</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -987,7 +987,7 @@
       </c>
       <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Clinic log-out Form</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS Plotted Activity Tracker</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac DNS AM Schedule Tracker</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Servicing Scorecard</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac Coaching Logs</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac RDOT Incentive</v>
+        <v>Updated as of 12/08/2025</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>WNS PennyMac SM DNP &amp; Productivity Incentive</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,7 +1091,7 @@
         <v>46001</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" ref="D3:D55" si="1">IF(OR(C30="-",C30=""),"",$C$1&amp;" "&amp;TEXT(C30,"mm/dd/yyyy"))</f>
+        <f t="shared" si="0"/>
         <v>Updated as of 12/10/2025</v>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
         <v>46001</v>
       </c>
       <c r="D31" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 12/10/2025</v>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v>61</v>
       </c>
       <c r="D32" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>61</v>
       </c>
       <c r="D33" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>61</v>
       </c>
       <c r="D34" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         <v>61</v>
       </c>
       <c r="D35" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         <v>45982</v>
       </c>
       <c r="D36" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 11/21/2025</v>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
         <v>45986</v>
       </c>
       <c r="D37" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 11/25/2025</v>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         <v>45986</v>
       </c>
       <c r="D38" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 11/25/2025</v>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>45980</v>
       </c>
       <c r="D39" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 11/19/2025</v>
       </c>
     </row>
@@ -1241,8 +1241,8 @@
         <v>45987</v>
       </c>
       <c r="D40" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 11/26/2025</v>
+        <f>A40</f>
+        <v>Default Servicing Performance Review</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1256,8 +1256,8 @@
         <v>45986</v>
       </c>
       <c r="D41" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 11/25/2025</v>
+        <f t="shared" ref="D41:D55" si="1">A41</f>
+        <v>Billability Report</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Attendance Report</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D43" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Attendance Monitoring Report</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>VL Allocation</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1306,7 +1306,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Non-CS RDOT Tracker</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 11/29/2025</v>
+        <v>OT Tracker</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D47" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 11/19/2025</v>
+        <v>WNS PennyMac Non-CS Scorecard</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Attendance Incentive</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>Non-CS PennyMac Masterlist</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>Downtime Issue Tracker - CS</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>WNS PennyMac Servicing Outliers_Break and Lunch Report</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>WNS Pennymac Call Volume Trend</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,20 +1415,20 @@
       <c r="C53" s="2"/>
       <c r="D53" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Consolidated System Issue and No Station Tracker</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
-      <c r="D54" s="1" t="str">
+      <c r="D54" s="1">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D55" s="1" t="str">
+      <c r="D55" s="1">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA4F91-3197-459F-91BD-891AE25F2961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736A6E13-22E0-4190-A8AE-717D4DD18D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="70">
   <si>
     <t>Reports Name</t>
   </si>
@@ -672,11 +672,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D55" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -687,11 +687,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -702,11 +702,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -717,11 +717,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -747,11 +747,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>45999</v>
+        <v>46006</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>Updated as of 12/15/2025</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -777,11 +777,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/01/2025</v>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -792,11 +792,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/09/2025</v>
+        <v>Updated as of 12/15/2025</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -807,11 +807,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -822,11 +822,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -836,10 +836,12 @@
       <c r="B13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2">
+        <v>46008</v>
+      </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -849,10 +851,12 @@
       <c r="B14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2">
+        <v>46008</v>
+      </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,11 +912,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1028,11 +1032,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1072,12 +1076,12 @@
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>61</v>
+      <c r="C29" s="2">
+        <v>45996</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 12/05/2025</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,11 +1092,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1103,11 +1107,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,11 +1227,11 @@
         <v>63</v>
       </c>
       <c r="C39" s="2">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="D39" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/19/2025</v>
+        <v>Updated as of 12/11/2025</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1241,8 +1245,8 @@
         <v>45987</v>
       </c>
       <c r="D40" s="1" t="str">
-        <f>A40</f>
-        <v>Default Servicing Performance Review</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 11/26/2025</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,11 +1257,11 @@
         <v>63</v>
       </c>
       <c r="C41" s="2">
-        <v>45986</v>
+        <v>46003</v>
       </c>
       <c r="D41" s="1" t="str">
-        <f t="shared" ref="D41:D55" si="1">A41</f>
-        <v>Billability Report</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/12/2025</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1271,8 +1275,8 @@
         <v>61</v>
       </c>
       <c r="D42" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Attendance Report</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,8 +1287,8 @@
         <v>61</v>
       </c>
       <c r="D43" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Attendance Monitoring Report</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,8 +1299,8 @@
         <v>61</v>
       </c>
       <c r="D44" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>VL Allocation</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,8 +1309,8 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Non-CS RDOT Tracker</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,8 +1321,8 @@
         <v>45990</v>
       </c>
       <c r="D46" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>OT Tracker</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 11/29/2025</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,8 +1336,8 @@
         <v>45980</v>
       </c>
       <c r="D47" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>WNS PennyMac Non-CS Scorecard</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 11/19/2025</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1344,8 +1348,8 @@
         <v>61</v>
       </c>
       <c r="D48" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Attendance Incentive</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1356,11 +1360,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="D49" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Non-CS PennyMac Masterlist</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,11 +1375,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="D50" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Downtime Issue Tracker - CS</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/16/2025</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1386,11 +1390,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>WNS PennyMac Servicing Outliers_Break and Lunch Report</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/15/2025</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,11 +1405,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>WNS Pennymac Call Volume Trend</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1414,21 +1418,21 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Consolidated System Issue and No Station Tracker</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
-      <c r="D54" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D55" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736A6E13-22E0-4190-A8AE-717D4DD18D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFE3873-1CC2-4874-BA80-7EBB8B382D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
   <si>
     <t>Reports Name</t>
   </si>
@@ -247,6 +247,24 @@
   </si>
   <si>
     <t>Consolidated System Issue and No Station Tracker</t>
+  </si>
+  <si>
+    <t>NON CS</t>
+  </si>
+  <si>
+    <t>Productivity &amp; AHT - Default</t>
+  </si>
+  <si>
+    <t>Productivity &amp; AHT - Non Default</t>
+  </si>
+  <si>
+    <t>SCC - Dialy Dialing Plan</t>
+  </si>
+  <si>
+    <t>Site Comparison Map</t>
+  </si>
+  <si>
+    <t>Attendance Monitoring Report - Non Default</t>
   </si>
 </sst>
 </file>
@@ -641,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1417,22 +1435,74 @@
         <v>69</v>
       </c>
       <c r="C53" s="2"/>
-      <c r="D53" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="2"/>
+      <c r="A54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46001</v>
+      </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" ref="D53:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 12/10/2025</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46008</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Updated as of 12/17/2025</v>
       </c>
     </row>
   </sheetData>
@@ -1481,8 +1551,13 @@
     <hyperlink ref="A51" r:id="rId42" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
     <hyperlink ref="A52" r:id="rId43" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
     <hyperlink ref="A53" r:id="rId44" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId45" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A56" r:id="rId46" xr:uid="{DBA89B55-106A-4499-A56B-A663EC6BA72B}"/>
+    <hyperlink ref="A57" r:id="rId47" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId48" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId49" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId45"/>
+  <pageSetup orientation="portrait" r:id="rId50"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFE3873-1CC2-4874-BA80-7EBB8B382D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3F39A1-7F9C-4BBD-95C7-0064EBEA630F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t>Reports Name</t>
   </si>
@@ -265,6 +265,18 @@
   </si>
   <si>
     <t>Attendance Monitoring Report - Non Default</t>
+  </si>
+  <si>
+    <t>Dept</t>
+  </si>
+  <si>
+    <t>Non-CS</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>CS</t>
   </si>
 </sst>
 </file>
@@ -659,16 +671,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="27.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1" hidden="1"/>
+    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -681,8 +694,11 @@
       <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -690,14 +706,17 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f t="shared" ref="D2:D55" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/16/2025</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -705,14 +724,17 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -720,14 +742,17 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -741,8 +766,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/16/2025</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -756,8 +784,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/08/2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -771,8 +802,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/15/2025</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
@@ -786,8 +820,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/03/2025</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
@@ -801,8 +838,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/10/2025</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
@@ -816,8 +856,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/15/2025</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -831,8 +874,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -846,8 +892,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -861,8 +910,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -876,8 +928,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -891,8 +946,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -906,8 +964,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
@@ -921,8 +982,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -930,14 +994,17 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
@@ -951,8 +1018,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
@@ -966,8 +1036,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
@@ -981,8 +1054,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>25</v>
       </c>
@@ -996,8 +1072,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
@@ -1011,8 +1090,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1026,8 +1108,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
@@ -1041,8 +1126,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
@@ -1050,14 +1138,17 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
@@ -1071,8 +1162,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
@@ -1086,8 +1180,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/08/2025</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -1101,8 +1198,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/05/2025</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
@@ -1116,8 +1216,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
@@ -1131,8 +1234,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
@@ -1146,8 +1252,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>36</v>
       </c>
@@ -1161,8 +1270,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -1176,8 +1288,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
@@ -1191,8 +1306,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>39</v>
       </c>
@@ -1206,8 +1324,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 11/21/2025</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>52</v>
       </c>
@@ -1215,14 +1336,17 @@
         <v>63</v>
       </c>
       <c r="C37" s="2">
-        <v>45986</v>
+        <v>46007</v>
       </c>
       <c r="D37" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/25/2025</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/16/2025</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>40</v>
       </c>
@@ -1236,8 +1360,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 11/25/2025</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>41</v>
       </c>
@@ -1251,8 +1378,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/11/2025</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -1266,8 +1396,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 11/26/2025</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>43</v>
       </c>
@@ -1281,8 +1414,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/12/2025</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -1296,8 +1432,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>45</v>
       </c>
@@ -1308,8 +1447,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>46</v>
       </c>
@@ -1320,8 +1462,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>47</v>
       </c>
@@ -1330,20 +1475,26 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="2">
-        <v>45990</v>
+        <v>45994</v>
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/29/2025</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/03/2025</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>49</v>
       </c>
@@ -1357,8 +1508,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 11/19/2025</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>50</v>
       </c>
@@ -1369,8 +1523,11 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>51</v>
       </c>
@@ -1384,8 +1541,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/17/2025</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>65</v>
       </c>
@@ -1399,8 +1559,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/16/2025</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>67</v>
       </c>
@@ -1414,8 +1577,11 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/15/2025</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>68</v>
       </c>
@@ -1429,14 +1595,26 @@
         <f t="shared" si="0"/>
         <v>Updated as of 12/10/2025</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="2">
+        <v>46011</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Updated as of 12/20/2025</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>71</v>
       </c>
@@ -1444,44 +1622,65 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D53:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/10/2025</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="C55" s="2">
+        <v>46008</v>
+      </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>73</v>
       </c>
+      <c r="C56" s="2">
+        <v>46009</v>
+      </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/18/2025</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>74</v>
       </c>
+      <c r="C57" s="2">
+        <v>46002</v>
+      </c>
       <c r="D57" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>Updated as of 12/11/2025</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>75</v>
       </c>
@@ -1489,8 +1688,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>51</v>
       </c>
@@ -1503,6 +1705,9 @@
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Updated as of 12/17/2025</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1556,8 +1761,9 @@
     <hyperlink ref="A57" r:id="rId47" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
     <hyperlink ref="A58" r:id="rId48" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
     <hyperlink ref="A59" r:id="rId49" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A54" r:id="rId50" xr:uid="{175BEC22-FB58-4245-B938-781F98DA0335}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId50"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3F39A1-7F9C-4BBD-95C7-0064EBEA630F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049E1E14-924E-405D-B32B-7DDC8B89E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049E1E14-924E-405D-B32B-7DDC8B89E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28DA97-FCEE-4282-8D10-9C722FB2CBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
   <si>
     <t>Reports Name</t>
   </si>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -1095,18 +1095,18 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>61</v>
+      <c r="C24" s="2">
+        <v>46009</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>79</v>
@@ -1762,8 +1762,9 @@
     <hyperlink ref="A58" r:id="rId48" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
     <hyperlink ref="A59" r:id="rId49" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
     <hyperlink ref="A54" r:id="rId50" xr:uid="{175BEC22-FB58-4245-B938-781F98DA0335}"/>
+    <hyperlink ref="A24" r:id="rId51" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId51"/>
+  <pageSetup orientation="portrait" r:id="rId52"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28DA97-FCEE-4282-8D10-9C722FB2CBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B5871A-9638-49C5-A5C4-CF4EFDF11F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
+        <v>Updated as of 12/22/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -778,11 +778,11 @@
         <v>54</v>
       </c>
       <c r="C6" s="2">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>79</v>
@@ -796,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46006</v>
+        <v>46013</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/15/2025</v>
+        <v>Updated as of 12/22/2025</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>79</v>
@@ -814,11 +814,11 @@
         <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>45994</v>
+        <v>46009</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/03/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1102,11 +1102,11 @@
         <v>61</v>
       </c>
       <c r="C24" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1174,11 +1174,11 @@
         <v>54</v>
       </c>
       <c r="C28" s="2">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/08/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46008</v>
+        <v>46013</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/22/2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
+        <v>Updated as of 12/22/2025</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1622,11 +1622,11 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1640,11 +1640,11 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
@@ -1655,11 +1655,11 @@
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1700,11 +1700,11 @@
         <v>64</v>
       </c>
       <c r="C59" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/17/2025</v>
+        <v>Updated as of 12/23/2025</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B5871A-9638-49C5-A5C4-CF4EFDF11F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB42314-A325-4EFB-BD10-39E40A9CCF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB42314-A325-4EFB-BD10-39E40A9CCF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C2C392-4D90-4BBC-BC56-6039DE82D100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1655,11 +1655,11 @@
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C2C392-4D90-4BBC-BC56-6039DE82D100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1119E1CD-9B69-4C6B-92BF-75CFD9AC7B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46013</v>
+        <v>46017</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/22/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -796,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/22/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1102,11 +1102,11 @@
         <v>61</v>
       </c>
       <c r="C24" s="2">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/24/2025</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/22/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1622,11 +1622,11 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1640,11 +1640,11 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/26/2025</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
@@ -1655,11 +1655,11 @@
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1700,11 +1700,11 @@
         <v>64</v>
       </c>
       <c r="C59" s="2">
-        <v>46014</v>
+        <v>46020</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/23/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1119E1CD-9B69-4C6B-92BF-75CFD9AC7B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBFCC00-C47C-4486-A8EB-0F40BA450E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBFCC00-C47C-4486-A8EB-0F40BA450E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A662A588-D004-4A58-9962-917FCC749DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/22/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A662A588-D004-4A58-9962-917FCC749DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1243179-244F-4CA1-8B25-A4588BD236DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -832,11 +832,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46001</v>
+        <v>46020</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1243179-244F-4CA1-8B25-A4588BD236DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2596D7F-15F6-40D3-AEAA-BF9215274CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46015</v>
+        <v>46021</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1102,11 +1102,11 @@
         <v>61</v>
       </c>
       <c r="C24" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/24/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1589,11 +1589,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46001</v>
+        <v>46021</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/10/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>79</v>
@@ -1622,11 +1622,11 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1655,11 +1655,11 @@
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1700,11 +1700,11 @@
         <v>64</v>
       </c>
       <c r="C59" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2596D7F-15F6-40D3-AEAA-BF9215274CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3176BE14-9C4A-4B0A-B096-449B3B7751C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -1640,11 +1640,11 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/26/2025</v>
+        <v>Updated as of 12/29/2025</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3176BE14-9C4A-4B0A-B096-449B3B7751C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D858F3C-EA7A-4F2E-AC4C-0A9F953A51D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -778,11 +778,11 @@
         <v>54</v>
       </c>
       <c r="C6" s="2">
-        <v>46009</v>
+        <v>45659</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 12/31/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 12/31/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,11 +1535,12 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46021</v>
+        <f>C59</f>
+        <v>45659</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1554,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 12/31/2025</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1615,18 +1616,18 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1640,26 +1641,26 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 12/31/2025</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1700,11 +1701,11 @@
         <v>64</v>
       </c>
       <c r="C59" s="2">
-        <v>46021</v>
+        <v>45659</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>
@@ -1757,12 +1758,12 @@
     <hyperlink ref="A52" r:id="rId43" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
     <hyperlink ref="A53" r:id="rId44" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
     <hyperlink ref="A55" r:id="rId45" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A56" r:id="rId46" xr:uid="{DBA89B55-106A-4499-A56B-A663EC6BA72B}"/>
-    <hyperlink ref="A57" r:id="rId47" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId48" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId49" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A54" r:id="rId50" xr:uid="{175BEC22-FB58-4245-B938-781F98DA0335}"/>
-    <hyperlink ref="A24" r:id="rId51" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A57" r:id="rId46" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId47" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId48" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId49" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId50" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId51" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId52"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D858F3C-EA7A-4F2E-AC4C-0A9F953A51D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9401C2-2C4E-451F-8A2E-2BEA70CB6ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -850,11 +850,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>46006</v>
+        <v>45662</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/15/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>46022</v>
+        <v>45659</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/31/2025</v>
+        <v>Updated as of 01/02/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>46022</v>
+        <v>45662</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/31/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,12 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <f>C59</f>
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1605,11 +1604,11 @@
         <v>69</v>
       </c>
       <c r="C53" s="2">
-        <v>46011</v>
+        <v>46009</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/20/2025</v>
+        <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>79</v>
@@ -1656,11 +1655,12 @@
         <v>73</v>
       </c>
       <c r="C56" s="2">
-        <v>46022</v>
+        <f ca="1">TODAY()</f>
+        <v>46027</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 12/31/2025</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>Updated as of 01/05/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1701,11 +1701,12 @@
         <v>64</v>
       </c>
       <c r="C59" s="2">
-        <v>45659</v>
+        <f>C49</f>
+        <v>45662</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9401C2-2C4E-451F-8A2E-2BEA70CB6ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632F3AE3-A78A-4368-8E70-4652CC659E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
   <si>
     <t>Reports Name</t>
   </si>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>45659</v>
+        <v>46028</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>45659</v>
+        <v>46028</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -796,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46020</v>
+        <v>45662</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/05/2025</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>45659</v>
+        <v>46028</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -957,12 +957,12 @@
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
+      <c r="C16" s="2">
+        <v>46028</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/31/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1571,11 +1571,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46006</v>
+        <v>46028</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/15/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>79</v>
@@ -1589,11 +1589,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>79</v>
@@ -1622,11 +1622,11 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>45659</v>
+        <v>46028</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1640,11 +1640,11 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>45659</v>
+        <v>46028</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/05/2026</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1702,11 +1702,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>45662</v>
+        <v>46028</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632F3AE3-A78A-4368-8E70-4652CC659E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A657D7-BC10-4CED-9C95-9360600123DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -753,18 +753,18 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46020</v>
+        <v>46028</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>46028</v>
+        <v>45664</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>46028</v>
+        <v>45664</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>46028</v>
+        <v>45664</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>45659</v>
+        <v>45664</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>45662</v>
+        <v>45664</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>46028</v>
+        <v>45664</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1571,11 +1571,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>79</v>
@@ -1622,11 +1622,11 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1718,53 +1718,53 @@
     <hyperlink ref="A26" r:id="rId2" xr:uid="{40541382-6428-4A46-B540-46C908B996ED}"/>
     <hyperlink ref="A31" r:id="rId3" xr:uid="{3FEA4DE8-A9E6-4999-B04C-CF819C94EEFF}"/>
     <hyperlink ref="A11" r:id="rId4" xr:uid="{48EEBA3C-D3F5-47CD-95C2-40A7DE08A55A}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{A3C5FC6A-3584-443D-BE21-4F35090CA933}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{85906350-3823-4627-86C0-7D220608E4F6}"/>
-    <hyperlink ref="A10" r:id="rId7" xr:uid="{FE1C16F4-D8E2-4FCC-95E8-0F17398E05AD}"/>
-    <hyperlink ref="A3" r:id="rId8" xr:uid="{9937AFC8-6550-4A66-BFE9-F6282B72E021}"/>
-    <hyperlink ref="A4" r:id="rId9" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
-    <hyperlink ref="A6" r:id="rId10" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
-    <hyperlink ref="A7" r:id="rId11" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
-    <hyperlink ref="A8" r:id="rId12" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
-    <hyperlink ref="A12" r:id="rId13" xr:uid="{A7A7ED68-7475-4DC9-ADD5-EBCAE400ADFD}"/>
-    <hyperlink ref="A13" r:id="rId14" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
-    <hyperlink ref="A14" r:id="rId15" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
-    <hyperlink ref="A15" r:id="rId16" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
-    <hyperlink ref="A16" r:id="rId17" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
-    <hyperlink ref="A17" r:id="rId18" xr:uid="{8EEC9744-8C7E-42D5-922B-939CC8C06606}"/>
-    <hyperlink ref="A50" r:id="rId19" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
-    <hyperlink ref="A18" r:id="rId20" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
-    <hyperlink ref="A19" r:id="rId21" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
-    <hyperlink ref="A20" r:id="rId22" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
-    <hyperlink ref="A21" r:id="rId23" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
-    <hyperlink ref="A27" r:id="rId24" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
-    <hyperlink ref="A28" r:id="rId25" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
-    <hyperlink ref="A29" r:id="rId26" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
-    <hyperlink ref="A30" r:id="rId27" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
-    <hyperlink ref="A36" r:id="rId28" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
-    <hyperlink ref="A37" r:id="rId29" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A38" r:id="rId30" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A39" r:id="rId31" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId32" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId33" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId34" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId35" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId36" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId37" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId38" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId39" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId40" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId41" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A51" r:id="rId42" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
-    <hyperlink ref="A52" r:id="rId43" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId44" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId45" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId46" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId47" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId48" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId49" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId50" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId51" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{85906350-3823-4627-86C0-7D220608E4F6}"/>
+    <hyperlink ref="A10" r:id="rId6" xr:uid="{FE1C16F4-D8E2-4FCC-95E8-0F17398E05AD}"/>
+    <hyperlink ref="A3" r:id="rId7" xr:uid="{9937AFC8-6550-4A66-BFE9-F6282B72E021}"/>
+    <hyperlink ref="A4" r:id="rId8" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
+    <hyperlink ref="A7" r:id="rId10" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
+    <hyperlink ref="A8" r:id="rId11" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
+    <hyperlink ref="A12" r:id="rId12" xr:uid="{A7A7ED68-7475-4DC9-ADD5-EBCAE400ADFD}"/>
+    <hyperlink ref="A13" r:id="rId13" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
+    <hyperlink ref="A14" r:id="rId14" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
+    <hyperlink ref="A15" r:id="rId15" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
+    <hyperlink ref="A16" r:id="rId16" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
+    <hyperlink ref="A17" r:id="rId17" xr:uid="{8EEC9744-8C7E-42D5-922B-939CC8C06606}"/>
+    <hyperlink ref="A50" r:id="rId18" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
+    <hyperlink ref="A18" r:id="rId19" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
+    <hyperlink ref="A19" r:id="rId20" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
+    <hyperlink ref="A20" r:id="rId21" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
+    <hyperlink ref="A21" r:id="rId22" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
+    <hyperlink ref="A27" r:id="rId23" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
+    <hyperlink ref="A28" r:id="rId24" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
+    <hyperlink ref="A29" r:id="rId25" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
+    <hyperlink ref="A30" r:id="rId26" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
+    <hyperlink ref="A36" r:id="rId27" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
+    <hyperlink ref="A37" r:id="rId28" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
+    <hyperlink ref="A38" r:id="rId29" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A39" r:id="rId30" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId31" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId32" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId33" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId34" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId35" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId36" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId37" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId38" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId39" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId40" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A51" r:id="rId41" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
+    <hyperlink ref="A52" r:id="rId42" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId43" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId44" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId45" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId46" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId47" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId48" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId49" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId50" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId51" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId52"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A657D7-BC10-4CED-9C95-9360600123DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1BE53A-1DB1-41E7-BA3C-CC9C028A0C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46028</v>
+        <v>45665</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46028</v>
+        <v>45665</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46028</v>
+        <v>45665</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46028</v>
+        <v>45664</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -814,11 +814,11 @@
         <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>46009</v>
+        <v>45665</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>
@@ -850,11 +850,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>45662</v>
+        <v>45665</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -958,11 +958,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>46028</v>
+        <v>45665</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>45659</v>
+        <v>45665</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1192,11 +1192,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>45996</v>
+        <v>45665</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/05/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>45662</v>
+        <v>45665</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1571,11 +1571,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2026</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>79</v>
@@ -1604,11 +1604,11 @@
         <v>69</v>
       </c>
       <c r="C53" s="2">
-        <v>46009</v>
+        <v>46376</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 12/20/2026</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>79</v>
@@ -1622,11 +1622,12 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <v>46029</v>
+        <f ca="1">TODAY()</f>
+        <v>46030</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/07/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1640,11 +1641,12 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <v>46028</v>
+        <f ca="1">TODAY()</f>
+        <v>46030</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 01/06/2026</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
@@ -1656,11 +1658,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/07/2026</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1702,11 +1704,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/07/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1BE53A-1DB1-41E7-BA3C-CC9C028A0C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6926FE-C9F1-46BD-97A4-A0E2608C2186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6926FE-C9F1-46BD-97A4-A0E2608C2186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A15D1C-AAC0-49C6-B918-8036E058FE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -778,11 +778,11 @@
         <v>54</v>
       </c>
       <c r="C6" s="2">
-        <v>45659</v>
+        <v>45666</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/02/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>79</v>
@@ -814,11 +814,11 @@
         <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>
@@ -850,11 +850,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>79</v>
@@ -868,11 +868,11 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
@@ -886,11 +886,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1336,11 +1336,11 @@
         <v>63</v>
       </c>
       <c r="C37" s="2">
-        <v>46007</v>
+        <v>45666</v>
       </c>
       <c r="D37" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/16/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>77</v>
@@ -1354,11 +1354,11 @@
         <v>63</v>
       </c>
       <c r="C38" s="2">
-        <v>45986</v>
+        <v>45666</v>
       </c>
       <c r="D38" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/25/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>77</v>
@@ -1372,11 +1372,11 @@
         <v>63</v>
       </c>
       <c r="C39" s="2">
-        <v>46002</v>
+        <v>45666</v>
       </c>
       <c r="D39" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/11/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>77</v>
@@ -1390,11 +1390,11 @@
         <v>63</v>
       </c>
       <c r="C40" s="2">
-        <v>45987</v>
+        <v>45666</v>
       </c>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/26/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>77</v>
@@ -1408,11 +1408,11 @@
         <v>63</v>
       </c>
       <c r="C41" s="2">
-        <v>46003</v>
+        <v>45666</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/12/2025</v>
+        <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>77</v>
@@ -1502,11 +1502,11 @@
         <v>63</v>
       </c>
       <c r="C47" s="2">
-        <v>45980</v>
+        <v>45665</v>
       </c>
       <c r="D47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/19/2025</v>
+        <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>77</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/07/2026</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1623,11 +1623,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>77</v>
@@ -1642,11 +1642,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>77</v>
@@ -1658,11 +1658,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/07/2026</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>
@@ -1744,29 +1744,29 @@
     <hyperlink ref="A30" r:id="rId26" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
     <hyperlink ref="A36" r:id="rId27" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
     <hyperlink ref="A37" r:id="rId28" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A38" r:id="rId29" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A39" r:id="rId30" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId31" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId32" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId33" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId34" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId35" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId36" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId37" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId38" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId39" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId40" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A51" r:id="rId41" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
-    <hyperlink ref="A52" r:id="rId42" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId43" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId44" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId45" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId46" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId47" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId48" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId49" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId50" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId51" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A39" r:id="rId29" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId30" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId31" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId32" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId33" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId34" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId35" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId36" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId37" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId38" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId39" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A51" r:id="rId40" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
+    <hyperlink ref="A52" r:id="rId41" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId42" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId43" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId44" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId45" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId46" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId47" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId48" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId49" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId50" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId51" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId52"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A15D1C-AAC0-49C6-B918-8036E058FE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27317BCE-7181-417E-AC38-2500A626AA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -706,11 +706,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>79</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>79</v>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>
@@ -778,11 +778,11 @@
         <v>54</v>
       </c>
       <c r="C6" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>79</v>
@@ -796,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>45662</v>
+        <v>46027</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2025</v>
+        <v>Updated as of 01/05/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>79</v>
@@ -814,11 +814,11 @@
         <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>
@@ -850,11 +850,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>79</v>
@@ -868,29 +868,29 @@
         <v>56</v>
       </c>
       <c r="C11" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>79</v>
@@ -904,11 +904,11 @@
         <v>58</v>
       </c>
       <c r="C13" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>79</v>
@@ -922,11 +922,11 @@
         <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>79</v>
@@ -958,11 +958,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>45665</v>
+        <v>46030</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>79</v>
@@ -975,12 +975,12 @@
       <c r="B17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
+      <c r="C17" s="2">
+        <v>46028</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>79</v>
@@ -994,11 +994,11 @@
         <v>60</v>
       </c>
       <c r="C18" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>79</v>
@@ -1138,11 +1138,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>45665</v>
+        <v>46030</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
@@ -1210,11 +1210,11 @@
         <v>56</v>
       </c>
       <c r="C30" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>79</v>
@@ -1228,11 +1228,11 @@
         <v>62</v>
       </c>
       <c r="C31" s="2">
-        <v>45666</v>
+        <v>46034</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>79</v>
@@ -1317,12 +1317,12 @@
       <c r="B36" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="2">
-        <v>45982</v>
+      <c r="C36" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 11/21/2025</v>
+        <v/>
       </c>
       <c r="E36" s="1" t="s">
         <v>79</v>
@@ -1354,11 +1354,11 @@
         <v>63</v>
       </c>
       <c r="C38" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D38" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>77</v>
@@ -1372,11 +1372,11 @@
         <v>63</v>
       </c>
       <c r="C39" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D39" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>77</v>
@@ -1390,11 +1390,11 @@
         <v>63</v>
       </c>
       <c r="C40" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>77</v>
@@ -1408,11 +1408,11 @@
         <v>63</v>
       </c>
       <c r="C41" s="2">
-        <v>45666</v>
+        <v>46031</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>77</v>
@@ -1502,11 +1502,11 @@
         <v>63</v>
       </c>
       <c r="C47" s="2">
-        <v>45665</v>
+        <v>46030</v>
       </c>
       <c r="D47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>77</v>
@@ -1535,11 +1535,11 @@
         <v>64</v>
       </c>
       <c r="C49" s="2">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>77</v>
@@ -1553,11 +1553,11 @@
         <v>66</v>
       </c>
       <c r="C50" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>78</v>
@@ -1571,11 +1571,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>79</v>
@@ -1622,11 +1622,10 @@
         <v>70</v>
       </c>
       <c r="C54" s="2">
-        <f ca="1">TODAY()</f>
         <v>46031</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -1641,11 +1640,10 @@
         <v>70</v>
       </c>
       <c r="C55" s="2">
-        <f ca="1">TODAY()</f>
         <v>46031</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -1658,11 +1656,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>77</v>
@@ -1704,11 +1702,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>77</v>
@@ -1727,46 +1725,46 @@
     <hyperlink ref="A6" r:id="rId9" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
     <hyperlink ref="A7" r:id="rId10" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
     <hyperlink ref="A8" r:id="rId11" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
-    <hyperlink ref="A12" r:id="rId12" xr:uid="{A7A7ED68-7475-4DC9-ADD5-EBCAE400ADFD}"/>
-    <hyperlink ref="A13" r:id="rId13" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
-    <hyperlink ref="A14" r:id="rId14" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
-    <hyperlink ref="A15" r:id="rId15" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
-    <hyperlink ref="A16" r:id="rId16" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
-    <hyperlink ref="A17" r:id="rId17" xr:uid="{8EEC9744-8C7E-42D5-922B-939CC8C06606}"/>
-    <hyperlink ref="A50" r:id="rId18" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
-    <hyperlink ref="A18" r:id="rId19" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
-    <hyperlink ref="A19" r:id="rId20" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
-    <hyperlink ref="A20" r:id="rId21" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
-    <hyperlink ref="A21" r:id="rId22" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
-    <hyperlink ref="A27" r:id="rId23" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
-    <hyperlink ref="A29" r:id="rId25" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
-    <hyperlink ref="A30" r:id="rId26" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
-    <hyperlink ref="A36" r:id="rId27" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
-    <hyperlink ref="A37" r:id="rId28" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A39" r:id="rId29" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId30" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId31" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId32" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId33" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId34" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId35" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId36" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId37" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId38" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId39" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A51" r:id="rId40" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
-    <hyperlink ref="A52" r:id="rId41" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId42" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId43" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId44" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId45" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId46" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId47" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId48" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId49" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId50" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
-    <hyperlink ref="A38" r:id="rId51" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A13" r:id="rId12" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
+    <hyperlink ref="A14" r:id="rId13" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
+    <hyperlink ref="A15" r:id="rId14" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{8EEC9744-8C7E-42D5-922B-939CC8C06606}"/>
+    <hyperlink ref="A50" r:id="rId17" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
+    <hyperlink ref="A18" r:id="rId18" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
+    <hyperlink ref="A19" r:id="rId19" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
+    <hyperlink ref="A21" r:id="rId21" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
+    <hyperlink ref="A27" r:id="rId22" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
+    <hyperlink ref="A28" r:id="rId23" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
+    <hyperlink ref="A29" r:id="rId24" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
+    <hyperlink ref="A30" r:id="rId25" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
+    <hyperlink ref="A36" r:id="rId26" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
+    <hyperlink ref="A37" r:id="rId27" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
+    <hyperlink ref="A39" r:id="rId28" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId29" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId30" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId31" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId32" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId33" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId34" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId35" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId36" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId37" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId38" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A51" r:id="rId39" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
+    <hyperlink ref="A52" r:id="rId40" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId41" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId42" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId43" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId44" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId45" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId46" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId47" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId48" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId49" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId50" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A12" r:id="rId51" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId52"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27317BCE-7181-417E-AC38-2500A626AA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB82E7DA-57AC-4A8C-899A-17B815577BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -814,11 +814,11 @@
         <v>54</v>
       </c>
       <c r="C8" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB82E7DA-57AC-4A8C-899A-17B815577BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD4925-F702-428A-B257-48CA3D99CDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -832,11 +832,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/29/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD4925-F702-428A-B257-48CA3D99CDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F5052-C466-48DC-9AE2-407686B67CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -796,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46027</v>
+        <v>46034</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/05/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F5052-C466-48DC-9AE2-407686B67CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916EE061-BB94-434B-9778-1798C5214661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -850,11 +850,11 @@
         <v>55</v>
       </c>
       <c r="C10" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916EE061-BB94-434B-9778-1798C5214661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1F3712-CFA8-4B0A-A536-642B9B617FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -1571,11 +1571,11 @@
         <v>59</v>
       </c>
       <c r="C51" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1F3712-CFA8-4B0A-A536-642B9B617FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C9762A-998E-40AA-9B37-3208A051D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -760,11 +760,11 @@
         <v>53</v>
       </c>
       <c r="C5" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>79</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C9762A-998E-40AA-9B37-3208A051D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B301AF-3DCC-46E3-B369-BC06A76EC8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$59</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="83">
   <si>
     <t>Reports Name</t>
   </si>
@@ -105,9 +108,6 @@
     <t>WNS PennyMac Consolidated System Issue Report -</t>
   </si>
   <si>
-    <t>WNS PennyMac Servicing Multiple Log-out Instance Report</t>
-  </si>
-  <si>
     <t>WNS PennyMac Proper Log Off EOD Report</t>
   </si>
   <si>
@@ -249,9 +249,6 @@
     <t>Consolidated System Issue and No Station Tracker</t>
   </si>
   <si>
-    <t>NON CS</t>
-  </si>
-  <si>
     <t>Productivity &amp; AHT - Default</t>
   </si>
   <si>
@@ -277,6 +274,21 @@
   </si>
   <si>
     <t>CS</t>
+  </si>
+  <si>
+    <t>Cadence</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>WNS BIllable Report</t>
   </si>
 </sst>
 </file>
@@ -671,17 +683,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="27.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1" hidden="1"/>
+    <col min="5" max="16383" width="9.140625" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -695,10 +707,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -713,10 +728,13 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -731,10 +749,13 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -749,15 +770,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2">
         <v>46034</v>
@@ -767,15 +791,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2">
         <v>46031</v>
@@ -785,10 +812,13 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -803,15 +833,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2">
         <v>46034</v>
@@ -821,10 +854,13 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
@@ -839,15 +875,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2">
         <v>46034</v>
@@ -857,15 +896,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2">
         <v>46034</v>
@@ -875,15 +917,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="2">
         <v>46034</v>
@@ -893,15 +938,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2">
         <v>46034</v>
@@ -911,15 +959,18 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2">
         <v>46034</v>
@@ -929,28 +980,34 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -965,15 +1022,18 @@
         <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2">
         <v>46028</v>
@@ -983,15 +1043,18 @@
         <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2">
         <v>46034</v>
@@ -1001,105 +1064,117 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46034</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Updated as of 01/12/2026</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="1" t="str">
+      <c r="B20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="1" t="str">
+      <c r="B21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="1" t="str">
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="E22" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="1" t="str">
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="E23" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2">
         <v>46021</v>
@@ -1109,30 +1184,30 @@
         <v>Updated as of 12/30/2025</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
@@ -1145,33 +1220,33 @@
         <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="2">
         <v>46009</v>
@@ -1181,12 +1256,12 @@
         <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>3</v>
@@ -1199,141 +1274,141 @@
         <v>Updated as of 01/08/2025</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46034</v>
+      </c>
+      <c r="D30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Updated as of 01/12/2026</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="2">
-        <v>46034</v>
-      </c>
-      <c r="D30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46034</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Updated as of 01/12/2026</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="2">
-        <v>46034</v>
-      </c>
-      <c r="D31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E32" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E33" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E34" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E35" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E36" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>45666</v>
@@ -1343,15 +1418,15 @@
         <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>46031</v>
@@ -1361,15 +1436,15 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>46031</v>
@@ -1379,15 +1454,15 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>46031</v>
@@ -1397,15 +1472,15 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>46031</v>
@@ -1415,60 +1490,69 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E42" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D43" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E43" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E44" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
@@ -1476,12 +1560,15 @@
         <v/>
       </c>
       <c r="E45" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C46" s="2">
         <v>45994</v>
@@ -1491,15 +1578,15 @@
         <v>Updated as of 12/03/2025</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>46030</v>
@@ -1509,30 +1596,33 @@
         <v>Updated as of 01/08/2026</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E48" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C49" s="2">
         <v>46034</v>
@@ -1542,16 +1632,16 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C50" s="2">
         <v>46034</v>
       </c>
@@ -1560,15 +1650,15 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51" s="2">
         <v>46034</v>
@@ -1578,12 +1668,12 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
@@ -1596,12 +1686,12 @@
         <v>Updated as of 01/06/2026</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" s="2">
         <v>46376</v>
@@ -1611,15 +1701,15 @@
         <v>Updated as of 12/20/2026</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C54" s="2">
         <v>46031</v>
@@ -1629,15 +1719,15 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C55" s="2">
         <v>46031</v>
@@ -1647,12 +1737,15 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
@@ -1663,12 +1756,15 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C57" s="2">
         <v>46002</v>
@@ -1678,27 +1774,30 @@
         <v>Updated as of 12/11/2025</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="D58" s="1" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" s="2">
         <f>C49</f>
@@ -1709,7 +1808,7 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B301AF-3DCC-46E3-B369-BC06A76EC8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ABB06B-E8ED-4C8C-96FE-D3DBADC6538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="83">
   <si>
     <t>Reports Name</t>
   </si>
@@ -721,11 +721,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>77</v>
@@ -742,11 +742,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>77</v>
@@ -763,11 +763,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>77</v>
@@ -784,11 +784,11 @@
         <v>52</v>
       </c>
       <c r="C5" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>77</v>
@@ -805,11 +805,11 @@
         <v>53</v>
       </c>
       <c r="C6" s="2">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>77</v>
@@ -910,11 +910,11 @@
         <v>55</v>
       </c>
       <c r="C11" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>77</v>
@@ -931,11 +931,11 @@
         <v>56</v>
       </c>
       <c r="C12" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>77</v>
@@ -952,11 +952,11 @@
         <v>57</v>
       </c>
       <c r="C13" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>77</v>
@@ -973,11 +973,11 @@
         <v>57</v>
       </c>
       <c r="C14" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>77</v>
@@ -1057,11 +1057,11 @@
         <v>59</v>
       </c>
       <c r="C18" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>77</v>
@@ -1078,11 +1078,11 @@
         <v>61</v>
       </c>
       <c r="C19" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>77</v>
@@ -1213,11 +1213,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>77</v>
@@ -1267,11 +1267,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>45665</v>
+        <v>46034</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2025</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>77</v>
@@ -1303,11 +1303,11 @@
         <v>61</v>
       </c>
       <c r="C31" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>77</v>
@@ -1625,11 +1625,11 @@
         <v>63</v>
       </c>
       <c r="C49" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>75</v>
@@ -1643,11 +1643,11 @@
         <v>65</v>
       </c>
       <c r="C50" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>76</v>
@@ -1679,11 +1679,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>77</v>
@@ -1693,12 +1693,12 @@
       <c r="A53" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="2">
-        <v>46376</v>
+      <c r="C53" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/20/2026</v>
+        <v/>
       </c>
       <c r="E53" s="1" t="s">
         <v>77</v>
@@ -1712,11 +1712,11 @@
         <v>60</v>
       </c>
       <c r="C54" s="2">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>75</v>
@@ -1730,11 +1730,11 @@
         <v>60</v>
       </c>
       <c r="C55" s="2">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>75</v>
@@ -1749,11 +1749,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>75</v>
@@ -1801,11 +1801,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>75</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ABB06B-E8ED-4C8C-96FE-D3DBADC6538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25030DB5-9F34-4844-80B5-9C2E7943777E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -847,11 +847,11 @@
         <v>53</v>
       </c>
       <c r="C8" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>77</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25030DB5-9F34-4844-80B5-9C2E7943777E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69522856-8A78-4AD3-ACC9-625D10E8E961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="83">
   <si>
     <t>Reports Name</t>
   </si>
@@ -805,11 +805,11 @@
         <v>53</v>
       </c>
       <c r="C6" s="2">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>77</v>
@@ -889,11 +889,11 @@
         <v>54</v>
       </c>
       <c r="C10" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>77</v>
@@ -910,11 +910,11 @@
         <v>55</v>
       </c>
       <c r="C11" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>77</v>
@@ -931,11 +931,11 @@
         <v>56</v>
       </c>
       <c r="C12" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>77</v>
@@ -952,11 +952,11 @@
         <v>57</v>
       </c>
       <c r="C13" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>77</v>
@@ -973,11 +973,11 @@
         <v>57</v>
       </c>
       <c r="C14" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>77</v>
@@ -1015,11 +1015,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>77</v>
@@ -1036,11 +1036,11 @@
         <v>58</v>
       </c>
       <c r="C17" s="2">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/06/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>77</v>
@@ -1057,11 +1057,11 @@
         <v>59</v>
       </c>
       <c r="C18" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>77</v>
@@ -1176,12 +1176,12 @@
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="2">
-        <v>46021</v>
+      <c r="C24" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/30/2025</v>
+        <v/>
       </c>
       <c r="E24" s="1" t="s">
         <v>77</v>
@@ -1285,11 +1285,11 @@
         <v>55</v>
       </c>
       <c r="C30" s="2">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>77</v>
@@ -1303,11 +1303,11 @@
         <v>61</v>
       </c>
       <c r="C31" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>77</v>
@@ -1625,11 +1625,11 @@
         <v>63</v>
       </c>
       <c r="C49" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>75</v>
@@ -1643,11 +1643,11 @@
         <v>65</v>
       </c>
       <c r="C50" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>76</v>
@@ -1661,11 +1661,11 @@
         <v>58</v>
       </c>
       <c r="C51" s="2">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>77</v>
@@ -1749,11 +1749,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>75</v>
@@ -1766,12 +1766,12 @@
       <c r="B57" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="2">
-        <v>46002</v>
+      <c r="C57" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D57" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 12/11/2025</v>
+        <v/>
       </c>
       <c r="E57" s="1" t="s">
         <v>75</v>
@@ -1801,11 +1801,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>75</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69522856-8A78-4AD3-ACC9-625D10E8E961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91352AC-6EEA-432A-BF9D-07B203F9A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="84">
   <si>
     <t>Reports Name</t>
   </si>
@@ -186,9 +186,6 @@
     <t>OT Tracker</t>
   </si>
   <si>
-    <t>WNS PennyMac Non-CS Scorecard</t>
-  </si>
-  <si>
     <t>Attendance Incentive</t>
   </si>
   <si>
@@ -289,6 +286,12 @@
   </si>
   <si>
     <t>WNS BIllable Report</t>
+  </si>
+  <si>
+    <t>WNS PennyMac Default Scorecard</t>
+  </si>
+  <si>
+    <t>WNS PennyMac Non-Default Scorecard</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -707,10 +710,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -728,10 +731,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -749,10 +752,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,10 +773,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -781,7 +784,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2">
         <v>46035</v>
@@ -791,10 +794,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -802,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2">
         <v>46036</v>
@@ -812,10 +815,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -833,10 +836,10 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2">
         <v>46035</v>
@@ -854,10 +857,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -875,10 +878,10 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -886,7 +889,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2">
         <v>46035</v>
@@ -896,10 +899,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -907,7 +910,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2">
         <v>46036</v>
@@ -917,10 +920,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -928,7 +931,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2">
         <v>46036</v>
@@ -938,10 +941,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,7 +952,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2">
         <v>46036</v>
@@ -959,10 +962,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,7 +973,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2">
         <v>46036</v>
@@ -980,10 +983,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -991,20 +994,20 @@
         <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E15" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,10 +1025,10 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1033,7 +1036,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2">
         <v>46036</v>
@@ -1043,10 +1046,10 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1054,7 +1057,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2">
         <v>46036</v>
@@ -1064,18 +1067,18 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2">
         <v>46035</v>
@@ -1085,10 +1088,10 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,20 +1099,20 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1117,20 +1120,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1138,17 +1141,17 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1156,17 +1159,17 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1174,17 +1177,17 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E24" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,17 +1195,17 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1220,7 +1223,7 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1228,17 +1231,17 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E27" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1246,7 +1249,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2">
         <v>46009</v>
@@ -1256,7 +1259,7 @@
         <v>Updated as of 12/18/2025</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1274,7 +1277,7 @@
         <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1282,7 +1285,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2">
         <v>46036</v>
@@ -1292,7 +1295,7 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1300,7 +1303,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="2">
         <v>46036</v>
@@ -1310,7 +1313,7 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1318,17 +1321,17 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E32" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1336,17 +1339,17 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E33" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1354,17 +1357,17 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E34" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1372,17 +1375,17 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E35" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1390,25 +1393,25 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>45666</v>
@@ -1418,7 +1421,7 @@
         <v>Updated as of 01/09/2025</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1426,7 +1429,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>46031</v>
@@ -1436,7 +1439,7 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1444,7 +1447,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>46031</v>
@@ -1454,7 +1457,7 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1462,7 +1465,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>46031</v>
@@ -1472,7 +1475,7 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1480,7 +1483,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>46031</v>
@@ -1490,7 +1493,7 @@
         <v>Updated as of 01/09/2026</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1498,17 +1501,17 @@
         <v>43</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1516,17 +1519,17 @@
         <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D43" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E43" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1534,17 +1537,17 @@
         <v>45</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1552,7 +1555,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
@@ -1560,7 +1563,7 @@
         <v/>
       </c>
       <c r="E45" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1568,7 +1571,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C46" s="2">
         <v>45994</v>
@@ -1578,51 +1581,51 @@
         <v>Updated as of 12/03/2025</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="D47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/08/2026</v>
+        <v>Updated as of 01/12/2026</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E48" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>46036</v>
@@ -1632,15 +1635,15 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C50" s="2">
         <v>46036</v>
@@ -1650,15 +1653,15 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="2">
         <v>46035</v>
@@ -1668,12 +1671,12 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
@@ -1686,30 +1689,30 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E53" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" s="2">
         <v>46035</v>
@@ -1719,15 +1722,15 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C55" s="2">
         <v>46035</v>
@@ -1737,15 +1740,15 @@
         <v>Updated as of 01/13/2026</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
@@ -1756,48 +1759,48 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D57" s="1" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D58" s="1" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <f>C49</f>
@@ -1808,7 +1811,22 @@
         <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46031</v>
+      </c>
+      <c r="D60" s="1" t="str">
+        <f t="shared" ref="D60" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <v>Updated as of 01/09/2026</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1864,8 +1882,9 @@
     <hyperlink ref="A5" r:id="rId49" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
     <hyperlink ref="A38" r:id="rId50" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
     <hyperlink ref="A12" r:id="rId51" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
+    <hyperlink ref="A60" r:id="rId52" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId52"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91352AC-6EEA-432A-BF9D-07B203F9A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFF0159-A62D-4ADC-BB16-C8ECD97D0A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFF0159-A62D-4ADC-BB16-C8ECD97D0A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1113A9B3-0515-404B-B730-19A2ECA1CEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46035</v>
+        <v>46041</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -829,11 +829,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -871,11 +871,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46036</v>
+        <v>46042</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/20/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46035</v>
+        <v>46043</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46035</v>
+        <v>46043</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1252,11 +1252,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46009</v>
+        <v>46041</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/18/2025</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46035</v>
+        <v>46043</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/20/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1804,11 +1804,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1819,11 +1819,11 @@
         <v>83</v>
       </c>
       <c r="C60" s="2">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="D60" s="1" t="str">
         <f t="shared" ref="D60" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1113A9B3-0515-404B-B730-19A2ECA1CEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0313E9FE-7CDF-4932-8AB2-F7BCD6DDE8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/22/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/21/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/20/2026</v>
+        <v>Updated as of 01/22/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/22/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1032,7 +1032,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46043</v>
+        <v>46046</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/24/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46043</v>
+        <v>46046</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/24/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,29 +1646,29 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/22/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/13/2026</v>
+        <v>Updated as of 01/14/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46043</v>
+        <v>46046</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/24/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/20/2026</v>
+        <v>Updated as of 01/24/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,12 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46043</v>
+        <v>46046</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 01/21/2026</v>
+        <f t="shared" si="1"/>
+        <v>Updated as of 01/24/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1804,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1846,43 +1845,43 @@
     <hyperlink ref="A14" r:id="rId13" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
     <hyperlink ref="A15" r:id="rId14" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
     <hyperlink ref="A16" r:id="rId15" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{8EEC9744-8C7E-42D5-922B-939CC8C06606}"/>
-    <hyperlink ref="A50" r:id="rId17" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
-    <hyperlink ref="A18" r:id="rId18" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
-    <hyperlink ref="A19" r:id="rId19" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
-    <hyperlink ref="A20" r:id="rId20" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
-    <hyperlink ref="A21" r:id="rId21" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
-    <hyperlink ref="A27" r:id="rId22" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
-    <hyperlink ref="A28" r:id="rId23" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
-    <hyperlink ref="A29" r:id="rId24" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
-    <hyperlink ref="A30" r:id="rId25" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
-    <hyperlink ref="A36" r:id="rId26" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
-    <hyperlink ref="A37" r:id="rId27" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A39" r:id="rId28" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId29" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId30" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId31" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId32" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId33" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId34" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId35" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId36" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId37" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId38" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A51" r:id="rId39" xr:uid="{8EAFFD51-CC5E-45CD-BFF0-DA9630C5E2EC}"/>
-    <hyperlink ref="A52" r:id="rId40" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId41" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId42" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId43" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId44" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId45" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId46" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId47" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId48" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId49" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
-    <hyperlink ref="A38" r:id="rId50" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A12" r:id="rId51" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
-    <hyperlink ref="A60" r:id="rId52" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
+    <hyperlink ref="A50" r:id="rId16" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
+    <hyperlink ref="A18" r:id="rId17" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
+    <hyperlink ref="A27" r:id="rId21" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
+    <hyperlink ref="A28" r:id="rId22" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
+    <hyperlink ref="A29" r:id="rId23" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
+    <hyperlink ref="A30" r:id="rId24" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
+    <hyperlink ref="A36" r:id="rId25" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
+    <hyperlink ref="A37" r:id="rId26" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
+    <hyperlink ref="A39" r:id="rId27" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId28" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId29" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId30" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId31" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId32" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId33" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId34" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId35" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId36" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId37" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A52" r:id="rId38" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId39" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId40" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId41" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId42" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId43" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId44" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId45" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId46" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId47" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId48" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A12" r:id="rId49" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
+    <hyperlink ref="A60" r:id="rId50" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
+    <hyperlink ref="A17" r:id="rId51" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
+    <hyperlink ref="A51" r:id="rId52" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0313E9FE-7CDF-4932-8AB2-F7BCD6DDE8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416A4E16-9514-4640-8D21-AA886C93F3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -885,18 +885,18 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/22/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/22/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/21/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/24/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/24/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1486,11 +1486,11 @@
         <v>61</v>
       </c>
       <c r="C41" s="2">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/24/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/24/2026</v>
+        <v>Updated as of 01/23/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/24/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1802,12 +1802,11 @@
         <v>62</v>
       </c>
       <c r="C59" s="2">
-        <f>C49</f>
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1835,53 +1834,53 @@
     <hyperlink ref="A31" r:id="rId3" xr:uid="{3FEA4DE8-A9E6-4999-B04C-CF819C94EEFF}"/>
     <hyperlink ref="A11" r:id="rId4" xr:uid="{48EEBA3C-D3F5-47CD-95C2-40A7DE08A55A}"/>
     <hyperlink ref="A9" r:id="rId5" xr:uid="{85906350-3823-4627-86C0-7D220608E4F6}"/>
-    <hyperlink ref="A10" r:id="rId6" xr:uid="{FE1C16F4-D8E2-4FCC-95E8-0F17398E05AD}"/>
-    <hyperlink ref="A3" r:id="rId7" xr:uid="{9937AFC8-6550-4A66-BFE9-F6282B72E021}"/>
-    <hyperlink ref="A4" r:id="rId8" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
-    <hyperlink ref="A7" r:id="rId10" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
-    <hyperlink ref="A8" r:id="rId11" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
-    <hyperlink ref="A13" r:id="rId12" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
-    <hyperlink ref="A14" r:id="rId13" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
-    <hyperlink ref="A15" r:id="rId14" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
-    <hyperlink ref="A50" r:id="rId16" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
-    <hyperlink ref="A18" r:id="rId17" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
-    <hyperlink ref="A27" r:id="rId21" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
-    <hyperlink ref="A28" r:id="rId22" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
-    <hyperlink ref="A29" r:id="rId23" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
-    <hyperlink ref="A30" r:id="rId24" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
-    <hyperlink ref="A36" r:id="rId25" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
-    <hyperlink ref="A37" r:id="rId26" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A39" r:id="rId27" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId28" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId29" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId30" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId31" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId32" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId33" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId34" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId35" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId36" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId37" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A52" r:id="rId38" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId39" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId40" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId41" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId42" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId43" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId44" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId45" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId46" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId47" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
-    <hyperlink ref="A38" r:id="rId48" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A12" r:id="rId49" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
-    <hyperlink ref="A60" r:id="rId50" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
-    <hyperlink ref="A17" r:id="rId51" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
-    <hyperlink ref="A51" r:id="rId52" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
+    <hyperlink ref="A3" r:id="rId6" xr:uid="{9937AFC8-6550-4A66-BFE9-F6282B72E021}"/>
+    <hyperlink ref="A4" r:id="rId7" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
+    <hyperlink ref="A6" r:id="rId8" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
+    <hyperlink ref="A7" r:id="rId9" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
+    <hyperlink ref="A8" r:id="rId10" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
+    <hyperlink ref="A13" r:id="rId11" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
+    <hyperlink ref="A14" r:id="rId12" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
+    <hyperlink ref="A15" r:id="rId13" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
+    <hyperlink ref="A16" r:id="rId14" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
+    <hyperlink ref="A50" r:id="rId15" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
+    <hyperlink ref="A18" r:id="rId16" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
+    <hyperlink ref="A19" r:id="rId17" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
+    <hyperlink ref="A20" r:id="rId18" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
+    <hyperlink ref="A21" r:id="rId19" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
+    <hyperlink ref="A27" r:id="rId20" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
+    <hyperlink ref="A28" r:id="rId21" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
+    <hyperlink ref="A29" r:id="rId22" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
+    <hyperlink ref="A30" r:id="rId23" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
+    <hyperlink ref="A36" r:id="rId24" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
+    <hyperlink ref="A37" r:id="rId25" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
+    <hyperlink ref="A39" r:id="rId26" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId27" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId28" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId29" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId30" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId31" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId32" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId33" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId34" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId35" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId36" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A52" r:id="rId37" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId38" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId39" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId40" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId41" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId42" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId43" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId44" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId45" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId46" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId47" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A12" r:id="rId48" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
+    <hyperlink ref="A60" r:id="rId49" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
+    <hyperlink ref="A17" r:id="rId50" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
+    <hyperlink ref="A51" r:id="rId51" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
+    <hyperlink ref="A10" r:id="rId52" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416A4E16-9514-4640-8D21-AA886C93F3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C110950-78C6-4FB3-8A77-432B23E144DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/22/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -829,11 +829,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/27/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -871,11 +871,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/26/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/27/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/22/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46036</v>
+        <v>46049</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/27/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1802,11 +1802,11 @@
         <v>62</v>
       </c>
       <c r="C59" s="2">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C110950-78C6-4FB3-8A77-432B23E144DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D24BC6-2491-4013-B6A6-C5E6C6A90FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46049</v>
+        <v>47147</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/27/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1039,11 +1039,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46036</v>
+        <v>46050</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/28/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1060,11 +1060,11 @@
         <v>58</v>
       </c>
       <c r="C18" s="2">
-        <v>46036</v>
+        <v>47147</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/14/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46045</v>
+        <v>47147</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46049</v>
+        <v>47147</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/27/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1252,11 +1252,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/19/2026</v>
+        <v>Updated as of 01/27/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46050</v>
+        <v>47147</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2029</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1802,11 +1802,12 @@
         <v>62</v>
       </c>
       <c r="C59" s="2">
-        <v>46050</v>
+        <f>C49</f>
+        <v>46051</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 01/29/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D24BC6-2491-4013-B6A6-C5E6C6A90FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F642FD-2C3F-43F7-B236-8FCB8B6AE1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
   <si>
     <t>Reports Name</t>
   </si>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -829,11 +829,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -871,11 +871,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/26/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1060,11 +1060,11 @@
         <v>58</v>
       </c>
       <c r="C18" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>47147</v>
+        <v>46052</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 01/30/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>47147</v>
+        <v>46055</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1468,11 +1468,11 @@
         <v>61</v>
       </c>
       <c r="C40" s="2">
-        <v>46031</v>
+        <v>46052</v>
       </c>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v>Updated as of 01/30/2026</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>74</v>
@@ -1486,11 +1486,11 @@
         <v>61</v>
       </c>
       <c r="C41" s="2">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/23/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>74</v>
@@ -1503,12 +1503,12 @@
       <c r="B42" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>59</v>
+      <c r="C42" s="2">
+        <v>46055</v>
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>74</v>
@@ -1592,11 +1592,11 @@
         <v>61</v>
       </c>
       <c r="C47" s="2">
-        <v>46034</v>
+        <v>46052</v>
       </c>
       <c r="D47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 01/30/2026</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>74</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/02/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F642FD-2C3F-43F7-B236-8FCB8B6AE1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186034D9-6253-476A-8711-3877B2886362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/04/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/05/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1018,11 +1018,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>46034</v>
+        <v>46056</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 02/03/2026</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>76</v>
@@ -1039,11 +1039,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/28/2026</v>
+        <v>Updated as of 02/04/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/30/2026</v>
+        <v>Updated as of 02/05/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1252,11 +1252,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/27/2026</v>
+        <v>Updated as of 02/03/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1270,11 +1270,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>46034</v>
+        <v>46056</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/12/2026</v>
+        <v>Updated as of 02/03/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/27/2026</v>
+        <v>Updated as of 02/03/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186034D9-6253-476A-8711-3877B2886362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282839F4-0F11-4709-B028-C0FB5398E96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="84">
   <si>
     <t>Reports Name</t>
   </si>
@@ -1395,12 +1395,12 @@
       <c r="B36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>59</v>
+      <c r="C36" s="2">
+        <v>46059</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 02/06/2026</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>76</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282839F4-0F11-4709-B028-C0FB5398E96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34FB96B-CEEF-4A35-9EC2-6DD294DFA763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
   <si>
     <t>Reports Name</t>
   </si>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/05/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -829,11 +829,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -871,11 +871,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>47147</v>
+        <v>46062</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2029</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1059,12 +1059,12 @@
       <c r="B18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="2">
-        <v>46055</v>
+      <c r="C18" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v/>
       </c>
       <c r="E18" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/05/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46051</v>
+        <v>46062</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/29/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 02/09/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34FB96B-CEEF-4A35-9EC2-6DD294DFA763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8A1DE4-34A0-43E9-B389-5E58BD970E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/04/2026</v>
+        <v>Updated as of 02/12/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -808,11 +808,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/05/2026</v>
+        <v>Updated as of 02/11/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -829,11 +829,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -850,11 +850,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/05/2026</v>
+        <v>Updated as of 02/11/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -871,11 +871,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1039,11 +1039,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46057</v>
+        <v>46069</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/04/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/13/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1252,11 +1252,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46056</v>
+        <v>46063</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/03/2026</v>
+        <v>Updated as of 02/10/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/03/2026</v>
+        <v>Updated as of 02/13/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8A1DE4-34A0-43E9-B389-5E58BD970E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F203D49-A9AF-4E2C-9639-73B2306D61FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -724,11 +724,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +745,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +766,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +787,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/12/2026</v>
+        <v>Updated as of 02/17/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -892,11 +892,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/09/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +913,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +934,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +955,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +976,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1039,11 +1039,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1081,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1216,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/13/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1288,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1628,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/17/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/13/2026</v>
+        <v>Updated as of 02/17/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/17/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1751,11 +1751,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F203D49-A9AF-4E2C-9639-73B2306D61FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A879A6-5DB4-4862-BA42-B3F62ABB2C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="86">
   <si>
     <t>Reports Name</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t>WNS PennyMac Non-Default Scorecard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WNS Productivity Lost Hours </t>
+  </si>
+  <si>
+    <t>Lou</t>
   </si>
 </sst>
 </file>
@@ -686,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -724,11 +730,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -745,11 +751,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,11 +772,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -787,11 +793,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/17/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -850,11 +856,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/11/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -892,11 +898,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -913,11 +919,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -934,11 +940,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -955,11 +961,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -976,11 +982,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1039,11 +1045,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46071</v>
+        <v>46069</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/16/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1081,11 +1087,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1216,11 +1222,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1288,11 +1294,11 @@
         <v>54</v>
       </c>
       <c r="C30" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1312,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1628,11 +1634,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1652,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1715,11 +1721,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1739,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/17/2026</v>
+        <v>Updated as of 02/18/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1803,11 +1809,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1821,11 +1827,29 @@
         <v>46041</v>
       </c>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v>Updated as of 01/19/2026</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46070</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Updated as of 02/17/2026</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1882,8 +1906,9 @@
     <hyperlink ref="A17" r:id="rId50" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
     <hyperlink ref="A51" r:id="rId51" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
     <hyperlink ref="A10" r:id="rId52" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
+    <hyperlink ref="A61" r:id="rId53" xr:uid="{8AD3FE60-4361-4D93-A592-E973B624B54F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId53"/>
+  <pageSetup orientation="portrait" r:id="rId54"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A879A6-5DB4-4862-BA42-B3F62ABB2C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034C4B51-B703-4006-AA12-F79218E250A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -730,11 +730,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -751,11 +751,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -772,11 +772,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -814,11 +814,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/11/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -856,11 +856,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -919,11 +919,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -940,11 +940,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -961,11 +961,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -982,11 +982,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1222,11 +1222,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1312,11 +1312,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1634,11 +1634,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1652,11 +1652,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1721,11 +1721,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1739,11 +1739,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/19/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1757,11 +1757,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="C59" s="2">
         <f>C49</f>
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/20/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034C4B51-B703-4006-AA12-F79218E250A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC323A4-CDB3-437B-9403-3A42138FA316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Lou</t>
+  </si>
+  <si>
+    <t>Carl</t>
   </si>
 </sst>
 </file>
@@ -730,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -751,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -772,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -793,11 +796,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 02/26/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -835,11 +838,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/23/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -877,11 +880,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 02/23/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -919,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -940,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -961,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -982,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1087,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46072</v>
+        <v>46077</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1222,11 +1225,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1291,14 +1294,14 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C30" s="2">
-        <v>46072</v>
+        <v>46077</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1312,11 +1315,11 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1808,12 +1811,11 @@
         <v>62</v>
       </c>
       <c r="C59" s="2">
-        <f>C49</f>
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC323A4-CDB3-437B-9403-3A42138FA316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741FC795-1B9B-48E8-BEBC-003AC3C67566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -754,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -796,11 +796,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/26/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -922,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -943,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -964,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -985,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1422,12 +1422,10 @@
       <c r="B37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="2">
-        <v>45666</v>
-      </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2025</v>
+        <v/>
       </c>
       <c r="E37" s="1" t="s">
         <v>74</v>
@@ -1440,12 +1438,10 @@
       <c r="B38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="2">
-        <v>46031</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v/>
       </c>
       <c r="E38" s="1" t="s">
         <v>74</v>
@@ -1458,12 +1454,10 @@
       <c r="B39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="2">
-        <v>46031</v>
-      </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/09/2026</v>
+        <v/>
       </c>
       <c r="E39" s="1" t="s">
         <v>74</v>
@@ -1476,12 +1470,10 @@
       <c r="B40" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="2">
-        <v>46052</v>
-      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/30/2026</v>
+        <v/>
       </c>
       <c r="E40" s="1" t="s">
         <v>74</v>
@@ -1582,12 +1574,10 @@
       <c r="B46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="2">
-        <v>45994</v>
-      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 12/03/2025</v>
+        <v/>
       </c>
       <c r="E46" s="1" t="s">
         <v>74</v>
@@ -1600,12 +1590,10 @@
       <c r="B47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="2">
-        <v>46052</v>
-      </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 01/30/2026</v>
+        <v/>
       </c>
       <c r="E47" s="1" t="s">
         <v>74</v>
@@ -1637,11 +1625,11 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46073</v>
+        <v>46078</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1655,11 +1643,11 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46073</v>
+        <v>46078</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1673,11 +1661,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/17/2026</v>
+        <v>Updated as of 02/23/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1691,11 +1679,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/17/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1724,11 +1712,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1742,11 +1730,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46072</v>
+        <v>46077</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1760,11 +1748,11 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/20/2026</v>
+        <v>Updated as of 02/24/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1825,12 +1813,10 @@
       <c r="A60" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="2">
-        <v>46041</v>
-      </c>
+      <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
         <f t="shared" ref="D60:D61" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
-        <v>Updated as of 01/19/2026</v>
+        <v/>
       </c>
       <c r="E60" s="1" t="s">
         <v>74</v>
@@ -1844,11 +1830,11 @@
         <v>85</v>
       </c>
       <c r="C61" s="2">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>Updated as of 02/17/2026</v>
+        <v>Updated as of 02/25/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>76</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741FC795-1B9B-48E8-BEBC-003AC3C67566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F88F474-4D93-4D43-A759-DF58963F3C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -754,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -922,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -943,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -964,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -985,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 02/26/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1225,11 +1225,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/26/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1315,11 +1315,12 @@
         <v>60</v>
       </c>
       <c r="C31" s="2">
-        <v>46077</v>
+        <f ca="1">TODAY()</f>
+        <v>46080</v>
       </c>
       <c r="D31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1486,12 +1487,12 @@
       <c r="B41" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="2">
-        <v>46055</v>
+      <c r="C41" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v/>
       </c>
       <c r="E41" s="1" t="s">
         <v>74</v>
@@ -1504,12 +1505,12 @@
       <c r="B42" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="2">
-        <v>46055</v>
+      <c r="C42" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/02/2026</v>
+        <v/>
       </c>
       <c r="E42" s="1" t="s">
         <v>74</v>
@@ -1625,11 +1626,12 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <v>46078</v>
+        <f ca="1">TODAY()</f>
+        <v>46080</v>
       </c>
       <c r="D49" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1643,11 +1645,12 @@
         <v>64</v>
       </c>
       <c r="C50" s="2">
-        <v>46078</v>
+        <f ca="1">TODAY()</f>
+        <v>46080</v>
       </c>
       <c r="D50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1712,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/26/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1730,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 02/26/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1748,11 +1751,12 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46077</v>
+        <f ca="1">TODAY()</f>
+        <v>46080</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 02/24/2026</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1799,11 +1803,12 @@
         <v>62</v>
       </c>
       <c r="C59" s="2">
-        <v>46077</v>
+        <f ca="1">TODAY()</f>
+        <v>46080</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 02/24/2026</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>Updated as of 02/27/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F88F474-4D93-4D43-A759-DF58963F3C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8DDC83-06EC-4EFF-AB21-7F6EB62B6ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -754,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -796,11 +796,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -817,11 +817,11 @@
         <v>52</v>
       </c>
       <c r="C6" s="2">
-        <v>46072</v>
+        <v>46083</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -838,11 +838,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/23/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -859,11 +859,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46072</v>
+        <v>46083</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/19/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -880,11 +880,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/23/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -922,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -943,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -964,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -985,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1048,11 +1048,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46069</v>
+        <v>46083</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/16/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/26/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1225,11 +1225,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/26/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1627,11 +1627,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1682,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1715,11 +1715,11 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 02/26/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1733,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 02/26/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1804,11 +1804,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 02/27/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8DDC83-06EC-4EFF-AB21-7F6EB62B6ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA605892-4044-41E2-8518-F3D6AF337380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -754,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -901,11 +901,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/18/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -922,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -943,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -964,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -985,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1225,11 +1225,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/03/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1261,11 +1261,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46063</v>
+        <v>46083</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/10/2026</v>
+        <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1297,11 +1297,11 @@
         <v>86</v>
       </c>
       <c r="C30" s="2">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/24/2026</v>
+        <v>Updated as of 03/03/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1406,11 +1406,11 @@
         <v>56</v>
       </c>
       <c r="C36" s="2">
-        <v>46059</v>
+        <v>46085</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/06/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>76</v>
@@ -1627,11 +1627,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1715,11 +1715,12 @@
         <v>59</v>
       </c>
       <c r="C54" s="2">
-        <v>46083</v>
+        <f ca="1">TODAY()</f>
+        <v>46085</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/02/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1733,11 +1734,11 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/03/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1752,11 +1753,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1804,11 +1805,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1835,11 +1836,11 @@
         <v>85</v>
       </c>
       <c r="C61" s="2">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>Updated as of 02/25/2026</v>
+        <v>Updated as of 03/03/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>76</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA605892-4044-41E2-8518-F3D6AF337380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB477355-4107-4CA3-9F48-CCACFD3F9C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -754,11 +754,11 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -796,11 +796,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -922,11 +922,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -943,11 +943,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -964,11 +964,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -985,11 +985,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1090,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1225,11 +1225,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/03/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1261,11 +1261,11 @@
         <v>52</v>
       </c>
       <c r="C28" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>76</v>
@@ -1279,11 +1279,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>46056</v>
+        <v>46086</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/03/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>76</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1627,11 +1627,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1646,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1664,11 +1664,12 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46076</v>
+        <f ca="1">TODAY()</f>
+        <v>46086</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 02/23/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1716,11 +1717,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1734,11 +1735,12 @@
         <v>59</v>
       </c>
       <c r="C55" s="2">
-        <v>46084</v>
+        <f ca="1">TODAY()</f>
+        <v>46086</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Updated as of 03/03/2026</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1753,11 +1755,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1805,11 +1807,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB477355-4107-4CA3-9F48-CCACFD3F9C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269F36AC-19A8-43F6-A962-7B015E67742B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="88">
   <si>
     <t>Reports Name</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Carl</t>
+  </si>
+  <si>
+    <t>DC</t>
   </si>
 </sst>
 </file>
@@ -695,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -705,7 +708,7 @@
     <col min="16384" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -725,7 +728,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -733,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -746,19 +749,17 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
-        <v>46086</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v/>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -766,8 +767,11 @@
       <c r="F3" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -775,11 +779,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -788,7 +792,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -796,11 +800,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 03/06/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -809,7 +813,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -830,7 +834,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -838,11 +842,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -851,7 +855,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
@@ -872,7 +876,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
@@ -880,11 +884,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -893,7 +897,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -914,7 +918,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -922,11 +926,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -935,7 +939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
@@ -943,11 +947,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -956,7 +960,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -964,11 +968,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -977,7 +981,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -985,11 +989,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -998,7 +1002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -1019,7 +1023,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -1027,11 +1031,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>46056</v>
+        <v>46086</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 02/03/2026</v>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>76</v>
@@ -1090,11 +1094,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1225,11 +1229,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/07/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1316,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1627,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1646,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1665,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1717,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1736,11 +1740,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1755,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1807,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/09/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269F36AC-19A8-43F6-A962-7B015E67742B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37C6D67-CA5C-48ED-88BA-BFAD894774E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -779,11 +779,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -926,11 +926,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -947,11 +947,11 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -968,11 +968,11 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -989,11 +989,11 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1094,11 +1094,11 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1668,12 +1668,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1687,11 +1686,12 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46083</v>
+        <f ca="1">TODAY()</f>
+        <v>46091</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1759,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1842,11 +1842,12 @@
         <v>85</v>
       </c>
       <c r="C61" s="2">
-        <v>46084</v>
+        <f ca="1">TODAY()</f>
+        <v>46091</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>Updated as of 03/03/2026</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>76</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37C6D67-CA5C-48ED-88BA-BFAD894774E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7817A-A0E8-4087-A0CF-C453B7A44736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -779,11 +779,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -800,11 +800,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/06/2026</v>
+        <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -926,11 +926,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -947,11 +947,12 @@
         <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>46091</v>
+        <f ca="1">TODAY()</f>
+        <v>46092</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -968,11 +969,12 @@
         <v>56</v>
       </c>
       <c r="C13" s="2">
-        <v>46091</v>
+        <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
+        <v>46092</v>
       </c>
       <c r="D13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -989,11 +991,12 @@
         <v>56</v>
       </c>
       <c r="C14" s="2">
-        <v>46091</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46092</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1094,11 +1097,12 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <v>46091</v>
+        <f t="shared" ref="C19" ca="1" si="2">TODAY()</f>
+        <v>46092</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1320,11 +1324,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1631,11 +1635,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1650,11 +1654,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1687,11 +1691,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1721,11 +1725,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1740,11 +1744,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1758,11 +1762,10 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <f ca="1">TODAY()</f>
         <v>46091</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="3"/>
         <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -1780,7 +1783,7 @@
         <v>59</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1795,7 +1798,7 @@
         <v>59</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1811,11 +1814,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1827,7 +1830,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="4">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1842,11 +1845,10 @@
         <v>85</v>
       </c>
       <c r="C61" s="2">
-        <f ca="1">TODAY()</f>
         <v>46091</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="4"/>
         <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E61" s="1" t="s">

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7817A-A0E8-4087-A0CF-C453B7A44736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFC3A7B-1891-4EEC-A9CF-BA03BEA10AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -779,11 +779,12 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>46092</v>
+        <f>C2</f>
+        <v>46093</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -800,11 +801,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -905,11 +906,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -926,11 +927,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -948,11 +949,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -970,11 +971,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -992,11 +993,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1055,11 +1056,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1098,11 +1099,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="2">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1305,11 +1306,11 @@
         <v>86</v>
       </c>
       <c r="C30" s="2">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/03/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1324,11 +1325,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1635,11 +1636,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1654,11 +1655,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1672,11 +1673,11 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 03/11/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1691,11 +1692,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1725,11 +1726,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1744,11 +1745,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1762,11 +1763,12 @@
         <v>59</v>
       </c>
       <c r="C56" s="2">
-        <v>46091</v>
+        <f ca="1">TODAY()</f>
+        <v>46093</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>Updated as of 03/10/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1814,11 +1816,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFC3A7B-1891-4EEC-A9CF-BA03BEA10AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FF4A39-62E2-45D7-BB5B-F31C81C430CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="88">
   <si>
     <t>Reports Name</t>
   </si>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -780,11 +780,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -801,11 +801,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -864,11 +864,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46083</v>
+        <v>46097</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -885,11 +885,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>76</v>
@@ -927,11 +927,11 @@
         <v>54</v>
       </c>
       <c r="C11" s="2">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -949,11 +949,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -971,11 +971,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -993,11 +993,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1034,12 +1034,12 @@
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="2">
-        <v>46086</v>
+      <c r="C16" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v/>
       </c>
       <c r="E16" s="1" t="s">
         <v>76</v>
@@ -1056,11 +1056,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="2">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1234,11 +1234,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46088</v>
+        <v>46097</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/07/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1306,11 +1306,11 @@
         <v>86</v>
       </c>
       <c r="C30" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/12/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1325,11 +1325,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1414,12 +1414,12 @@
       <c r="B36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="2">
-        <v>46085</v>
+      <c r="C36" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v/>
       </c>
       <c r="E36" s="1" t="s">
         <v>76</v>
@@ -1636,11 +1636,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1655,11 +1655,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1673,11 +1673,12 @@
         <v>57</v>
       </c>
       <c r="C51" s="2">
-        <v>46092</v>
+        <f ca="1">TODAY()</f>
+        <v>46097</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1692,11 +1693,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1726,11 +1727,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1745,11 +1746,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1764,11 +1765,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1816,11 +1817,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FF4A39-62E2-45D7-BB5B-F31C81C430CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7E078B-7CD5-4F14-AB8F-650B77040BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -780,11 +780,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -801,11 +801,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="2">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -843,11 +843,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/09/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -926,12 +926,10 @@
       <c r="B11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="2">
-        <v>46097</v>
-      </c>
+      <c r="C11" s="2"/>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v/>
       </c>
       <c r="E11" s="1" t="s">
         <v>76</v>
@@ -949,11 +947,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -971,11 +969,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -993,11 +991,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1099,11 +1097,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="2">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1234,11 +1232,12 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46097</v>
+        <f t="shared" ref="C26" ca="1" si="3">TODAY()</f>
+        <v>46099</v>
       </c>
       <c r="D26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1325,11 +1324,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1636,11 +1635,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1655,11 +1654,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1674,11 +1673,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1693,11 +1692,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1727,11 +1726,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1746,11 +1745,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1765,11 +1764,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1786,7 +1785,7 @@
         <v>59</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1801,7 +1800,7 @@
         <v>59</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1817,11 +1816,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 03/18/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1833,7 +1832,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="4">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="5">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1851,7 +1850,7 @@
         <v>46091</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E61" s="1" t="s">

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7E078B-7CD5-4F14-AB8F-650B77040BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F33CAC2-363E-4D55-853A-0B8680B2ABC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -736,11 +736,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -780,11 +780,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -864,11 +864,11 @@
         <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -906,11 +906,11 @@
         <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/11/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>76</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>76</v>
@@ -969,11 +969,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>76</v>
@@ -991,11 +991,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>76</v>
@@ -1054,11 +1054,12 @@
         <v>57</v>
       </c>
       <c r="C17" s="2">
-        <v>46097</v>
+        <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
+        <v>46100</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>76</v>
@@ -1096,12 +1097,12 @@
         <v>60</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" ref="C19" ca="1" si="2">TODAY()</f>
-        <v>46099</v>
+        <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
+        <v>46100</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>76</v>
@@ -1232,12 +1233,12 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" ref="C26" ca="1" si="3">TODAY()</f>
-        <v>46099</v>
+        <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
+        <v>46100</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>76</v>
@@ -1305,11 +1306,11 @@
         <v>86</v>
       </c>
       <c r="C30" s="2">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/12/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>76</v>
@@ -1324,11 +1325,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>76</v>
@@ -1635,11 +1636,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>74</v>
@@ -1654,11 +1655,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>75</v>
@@ -1673,11 +1674,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>76</v>
@@ -1692,11 +1693,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>76</v>
@@ -1726,11 +1727,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/18/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>74</v>
@@ -1745,11 +1746,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 03/18/2026</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>74</v>
@@ -1764,11 +1765,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 03/18/2026</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>74</v>
@@ -1785,7 +1786,7 @@
         <v>59</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1800,7 +1801,7 @@
         <v>59</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1816,11 +1817,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 03/18/2026</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>74</v>
@@ -1832,7 +1833,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="5">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="6">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1850,7 +1851,7 @@
         <v>46091</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Updated as of 03/10/2026</v>
       </c>
       <c r="E61" s="1" t="s">

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F33CAC2-363E-4D55-853A-0B8680B2ABC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DDE999-0E4E-4EA0-AF0C-AF8F000AD8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Ref</t>
   </si>
   <si>
-    <t>Performance Dashboard</t>
-  </si>
-  <si>
     <t>Productivity Dashboard</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t>WNS PennyMac Excessive Extended Wrap Report</t>
   </si>
   <si>
-    <t>WNS PennyMac Servicing AHT Trend</t>
-  </si>
-  <si>
     <t>WNS PennyMac Performance Trend</t>
   </si>
   <si>
@@ -304,6 +298,9 @@
   </si>
   <si>
     <t>DC</t>
+  </si>
+  <si>
+    <t>Shrinkage</t>
   </si>
 </sst>
 </file>
@@ -722,104 +719,99 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/20/2026</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2">
         <v>46083</v>
@@ -829,39 +821,39 @@
         <v>Updated as of 03/02/2026</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/18/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2">
         <v>46100</v>
@@ -871,15 +863,15 @@
         <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -892,18 +884,18 @@
         <v>Updated as of 03/16/2026</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2">
         <v>46100</v>
@@ -913,361 +905,363 @@
         <v>Updated as of 03/19/2026</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>12</v>
+      <c r="A11" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46104</v>
+      </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E22" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E23" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E24" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E25" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E27" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2">
         <v>46085</v>
@@ -1277,12 +1271,12 @@
         <v>Updated as of 03/04/2026</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>3</v>
@@ -1295,142 +1289,142 @@
         <v>Updated as of 03/05/2026</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E32" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E33" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E34" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E35" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E36" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="1" t="str">
@@ -1438,15 +1432,15 @@
         <v/>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="1" t="str">
@@ -1454,15 +1448,15 @@
         <v/>
       </c>
       <c r="E38" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="1" t="str">
@@ -1470,15 +1464,15 @@
         <v/>
       </c>
       <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="1" t="str">
@@ -1486,87 +1480,87 @@
         <v/>
       </c>
       <c r="E40" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E41" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E42" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D43" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E43" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E44" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1" t="str">
@@ -1574,15 +1568,15 @@
         <v/>
       </c>
       <c r="E45" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="1" t="str">
@@ -1590,15 +1584,15 @@
         <v/>
       </c>
       <c r="E46" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="1" t="str">
@@ -1606,230 +1600,230 @@
         <v/>
       </c>
       <c r="E47" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E48" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E53" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D57" s="1" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D58" s="1" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
@@ -1837,25 +1831,25 @@
         <v/>
       </c>
       <c r="E60" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C61" s="2">
-        <v>46091</v>
+        <v>46104</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>Updated as of 03/10/2026</v>
+        <v>Updated as of 03/23/2026</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1863,58 +1857,57 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{BE3B1711-F118-46E6-8721-176E46B5A9B8}"/>
     <hyperlink ref="A26" r:id="rId2" xr:uid="{40541382-6428-4A46-B540-46C908B996ED}"/>
     <hyperlink ref="A31" r:id="rId3" xr:uid="{3FEA4DE8-A9E6-4999-B04C-CF819C94EEFF}"/>
-    <hyperlink ref="A11" r:id="rId4" xr:uid="{48EEBA3C-D3F5-47CD-95C2-40A7DE08A55A}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{85906350-3823-4627-86C0-7D220608E4F6}"/>
-    <hyperlink ref="A3" r:id="rId6" xr:uid="{9937AFC8-6550-4A66-BFE9-F6282B72E021}"/>
-    <hyperlink ref="A4" r:id="rId7" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
-    <hyperlink ref="A6" r:id="rId8" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
-    <hyperlink ref="A7" r:id="rId9" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
-    <hyperlink ref="A8" r:id="rId10" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
-    <hyperlink ref="A13" r:id="rId11" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
-    <hyperlink ref="A14" r:id="rId12" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
-    <hyperlink ref="A15" r:id="rId13" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
-    <hyperlink ref="A16" r:id="rId14" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
-    <hyperlink ref="A50" r:id="rId15" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
-    <hyperlink ref="A18" r:id="rId16" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
-    <hyperlink ref="A19" r:id="rId17" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
-    <hyperlink ref="A20" r:id="rId18" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
-    <hyperlink ref="A21" r:id="rId19" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
-    <hyperlink ref="A27" r:id="rId20" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
-    <hyperlink ref="A28" r:id="rId21" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
-    <hyperlink ref="A29" r:id="rId22" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
-    <hyperlink ref="A30" r:id="rId23" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
-    <hyperlink ref="A36" r:id="rId24" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
-    <hyperlink ref="A37" r:id="rId25" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
-    <hyperlink ref="A39" r:id="rId26" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
-    <hyperlink ref="A40" r:id="rId27" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
-    <hyperlink ref="A41" r:id="rId28" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
-    <hyperlink ref="A47" r:id="rId29" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
-    <hyperlink ref="A48" r:id="rId30" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
-    <hyperlink ref="A42" r:id="rId31" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
-    <hyperlink ref="A43" r:id="rId32" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
-    <hyperlink ref="A44" r:id="rId33" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
-    <hyperlink ref="A45" r:id="rId34" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
-    <hyperlink ref="A46" r:id="rId35" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId36" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A52" r:id="rId37" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId38" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId39" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId40" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId41" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId42" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId43" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId44" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId45" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId46" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
-    <hyperlink ref="A38" r:id="rId47" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A12" r:id="rId48" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
-    <hyperlink ref="A60" r:id="rId49" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
-    <hyperlink ref="A17" r:id="rId50" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
-    <hyperlink ref="A51" r:id="rId51" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
-    <hyperlink ref="A10" r:id="rId52" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
-    <hyperlink ref="A61" r:id="rId53" xr:uid="{8AD3FE60-4361-4D93-A592-E973B624B54F}"/>
+    <hyperlink ref="A9" r:id="rId4" xr:uid="{85906350-3823-4627-86C0-7D220608E4F6}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{0FEA0474-3E19-44CE-BC47-ABCDEE360D95}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{A2FD74E7-ABF3-4F58-A5D0-B6BB4FB802DF}"/>
+    <hyperlink ref="A7" r:id="rId7" location="gid=1707523417" xr:uid="{7331DF90-1C5D-48E0-A1C5-460D90679373}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{0B08D417-46C5-44B2-8F21-1334D99ACB4B}"/>
+    <hyperlink ref="A13" r:id="rId9" location="gid=1069046833" xr:uid="{AF71E9C4-C797-4E2E-B25B-647817BE8307}"/>
+    <hyperlink ref="A14" r:id="rId10" location="gid=352498702" xr:uid="{45FDC326-08AA-4B16-9DA5-ADB1193732E2}"/>
+    <hyperlink ref="A15" r:id="rId11" location="gid=0" xr:uid="{EDAB5192-81A6-4D84-8C20-C13A71E593B1}"/>
+    <hyperlink ref="A16" r:id="rId12" xr:uid="{F4727829-C313-4070-8D41-B7A36EB11F0E}"/>
+    <hyperlink ref="A50" r:id="rId13" location="gid=2021441349" xr:uid="{941A9CD5-138E-4E42-8F2A-E508F6555852}"/>
+    <hyperlink ref="A18" r:id="rId14" location="gid=2018268353" xr:uid="{E2A9068D-D0F2-4C49-B086-82DB731A4845}"/>
+    <hyperlink ref="A19" r:id="rId15" xr:uid="{3BC8AA2A-3E4A-4AD6-8019-5473A5A5AB93}"/>
+    <hyperlink ref="A20" r:id="rId16" xr:uid="{513AFC13-AAF3-4006-8642-0AA335672BC3}"/>
+    <hyperlink ref="A21" r:id="rId17" xr:uid="{5F5908AC-366D-4E94-86D0-B872BAE52008}"/>
+    <hyperlink ref="A27" r:id="rId18" xr:uid="{069D8912-0246-4E59-B781-6C9D7FB984EE}"/>
+    <hyperlink ref="A28" r:id="rId19" xr:uid="{9EC9F904-F15A-4DB0-85E5-62CA6C40D62C}"/>
+    <hyperlink ref="A29" r:id="rId20" xr:uid="{839BB2A6-B17C-4090-B697-4C0EB5A398C5}"/>
+    <hyperlink ref="A30" r:id="rId21" xr:uid="{1D1B69A3-25E9-42F9-BD92-52D94950BD5C}"/>
+    <hyperlink ref="A36" r:id="rId22" xr:uid="{4B06A9EE-1ADC-498A-A119-799D0B564461}"/>
+    <hyperlink ref="A37" r:id="rId23" xr:uid="{9A0317B5-A70D-4871-A827-FA3E8B180DAB}"/>
+    <hyperlink ref="A39" r:id="rId24" xr:uid="{3B86774F-44DE-4523-8EED-50648467E59D}"/>
+    <hyperlink ref="A40" r:id="rId25" xr:uid="{DE8525EC-B2BF-48BA-9C50-6A790C06EB7C}"/>
+    <hyperlink ref="A41" r:id="rId26" xr:uid="{346316FB-7252-4F6E-8F59-DE8D85486D70}"/>
+    <hyperlink ref="A47" r:id="rId27" xr:uid="{9F2A4D38-5C85-44F2-8E48-3E91359DBDE2}"/>
+    <hyperlink ref="A48" r:id="rId28" xr:uid="{FB758336-C5BE-4D57-A5A8-C0AD6BFCD47F}"/>
+    <hyperlink ref="A42" r:id="rId29" xr:uid="{71817362-398D-4B10-8D45-EAEFB3B377E8}"/>
+    <hyperlink ref="A43" r:id="rId30" xr:uid="{50401DB3-DF59-4E1F-812A-99D16FB531F6}"/>
+    <hyperlink ref="A44" r:id="rId31" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
+    <hyperlink ref="A45" r:id="rId32" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
+    <hyperlink ref="A46" r:id="rId33" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
+    <hyperlink ref="A49" r:id="rId34" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
+    <hyperlink ref="A52" r:id="rId35" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId36" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId37" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId38" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId39" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId40" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId41" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId42" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId43" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId44" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId45" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A12" r:id="rId46" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
+    <hyperlink ref="A60" r:id="rId47" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
+    <hyperlink ref="A17" r:id="rId48" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
+    <hyperlink ref="A51" r:id="rId49" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
+    <hyperlink ref="A10" r:id="rId50" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
+    <hyperlink ref="A61" r:id="rId51" xr:uid="{8AD3FE60-4361-4D93-A592-E973B624B54F}"/>
+    <hyperlink ref="A11" r:id="rId52" xr:uid="{3DB4D4C3-5932-42C3-A654-AB0A6C2365D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId54"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DDE999-0E4E-4EA0-AF0C-AF8F000AD8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA86C86E-3AAC-427B-ACF4-4356BDDE21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/20/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -877,11 +877,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/16/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1300,11 +1300,12 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46104</v>
+        <f ca="1">TODAY()</f>
+        <v>46105</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1319,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1630,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1649,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1668,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1688,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1721,11 +1722,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1741,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1760,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1811,11 +1812,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA86C86E-3AAC-427B-ACF4-4356BDDE21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F546C3D0-6B4C-4E8A-BD86-D9E4EA95FECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -856,11 +856,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -898,11 +898,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/19/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1687,10 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <f ca="1">TODAY()</f>
         <v>46105</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1722,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1739,10 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <f ca="1">TODAY()</f>
         <v>46105</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>Updated as of 03/24/2026</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -1760,11 +1758,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1812,11 +1810,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F546C3D0-6B4C-4E8A-BD86-D9E4EA95FECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2858B2-4343-4441-B59A-6A1BBF5EE5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -898,11 +898,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1687,12 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46105</v>
+        <f ca="1">TODAY()</f>
+        <v>46107</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1721,11 +1722,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1739,11 +1740,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/25/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1758,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1810,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2858B2-4343-4441-B59A-6A1BBF5EE5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D162B115-029E-4546-A356-E943BFF81A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -814,11 +814,11 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/02/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1687,10 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <f ca="1">TODAY()</f>
         <v>46107</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 03/26/2026</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1722,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1739,12 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46106</v>
+        <f ca="1">TODAY()</f>
+        <v>46108</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>Updated as of 03/25/2026</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/27/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D162B115-029E-4546-A356-E943BFF81A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFDC152-C940-4D62-838A-6C36B6E40687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 03/31/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -835,11 +835,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 03/31/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>74</v>
@@ -856,11 +856,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/25/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -877,11 +877,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/24/2026</v>
+        <v>Updated as of 03/30/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -898,11 +898,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -919,11 +919,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46104</v>
+        <v>46113</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1687,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/26/2026</v>
+        <v>Updated as of 03/31/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1842,11 +1842,11 @@
         <v>83</v>
       </c>
       <c r="C61" s="2">
-        <v>46104</v>
+        <v>46113</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>Updated as of 03/23/2026</v>
+        <v>Updated as of 04/01/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFDC152-C940-4D62-838A-6C36B6E40687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E54788B-E454-4DFE-80DC-0E0E4D0C9DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/31/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -856,11 +856,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -898,11 +898,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E54788B-E454-4DFE-80DC-0E0E4D0C9DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2769DB-18AF-4BDD-8E16-0B68D85A4147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -733,11 +733,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +793,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/06/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -835,11 +835,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/31/2026</v>
+        <v>Updated as of 04/06/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>74</v>
@@ -877,11 +877,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/30/2026</v>
+        <v>Updated as of 04/06/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -919,11 +919,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/01/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -941,11 +941,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +985,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1227,11 +1227,10 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" ref="C26" ca="1" si="4">TODAY()</f>
         <v>46115</v>
       </c>
       <c r="D26" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1264,11 +1263,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46085</v>
+        <v>46115</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/04/2026</v>
+        <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1300,11 +1299,10 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <f ca="1">TODAY()</f>
         <v>46115</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>Updated as of 04/03/2026</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1320,11 +1318,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1629,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1648,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1668,12 +1666,11 @@
         <v>55</v>
       </c>
       <c r="C51" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1687,11 +1684,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/31/2026</v>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1720,12 +1717,11 @@
         <v>57</v>
       </c>
       <c r="C54" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="5">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/03/2026</v>
+        <f t="shared" ref="D54:D59" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 04/06/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1739,12 +1735,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/03/2026</v>
+        <f t="shared" si="4"/>
+        <v>Updated as of 04/06/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1754,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/03/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1780,7 +1775,7 @@
         <v>57</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1795,7 +1790,7 @@
         <v>57</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1811,11 +1806,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/03/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1827,7 +1822,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="6">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="5">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1842,11 +1837,11 @@
         <v>83</v>
       </c>
       <c r="C61" s="2">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>Updated as of 04/01/2026</v>
+        <f t="shared" si="5"/>
+        <v>Updated as of 04/07/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>
@@ -1887,25 +1882,25 @@
     <hyperlink ref="A44" r:id="rId31" xr:uid="{41777ADA-F44C-41C5-A37D-2D677531BD17}"/>
     <hyperlink ref="A45" r:id="rId32" xr:uid="{27525080-6F88-41CE-9C0F-596A6C278894}"/>
     <hyperlink ref="A46" r:id="rId33" xr:uid="{82477025-71C6-425C-B0C3-F95D01408905}"/>
-    <hyperlink ref="A49" r:id="rId34" xr:uid="{1CF4C930-9E20-4D0D-A1DC-0808B41DD26F}"/>
-    <hyperlink ref="A52" r:id="rId35" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
-    <hyperlink ref="A53" r:id="rId36" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
-    <hyperlink ref="A55" r:id="rId37" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
-    <hyperlink ref="A57" r:id="rId38" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
-    <hyperlink ref="A58" r:id="rId39" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
-    <hyperlink ref="A59" r:id="rId40" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
-    <hyperlink ref="A24" r:id="rId41" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
-    <hyperlink ref="A56" r:id="rId42" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
-    <hyperlink ref="A54" r:id="rId43" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
-    <hyperlink ref="A5" r:id="rId44" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
-    <hyperlink ref="A38" r:id="rId45" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
-    <hyperlink ref="A12" r:id="rId46" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
-    <hyperlink ref="A60" r:id="rId47" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
-    <hyperlink ref="A17" r:id="rId48" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
-    <hyperlink ref="A51" r:id="rId49" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
-    <hyperlink ref="A10" r:id="rId50" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
-    <hyperlink ref="A61" r:id="rId51" xr:uid="{8AD3FE60-4361-4D93-A592-E973B624B54F}"/>
-    <hyperlink ref="A11" r:id="rId52" xr:uid="{3DB4D4C3-5932-42C3-A654-AB0A6C2365D1}"/>
+    <hyperlink ref="A52" r:id="rId34" xr:uid="{A377EDCB-EB2E-4274-9157-9DC1A1A962EC}"/>
+    <hyperlink ref="A53" r:id="rId35" xr:uid="{63ED59C4-A25E-46DC-924D-B80C3709C42D}"/>
+    <hyperlink ref="A55" r:id="rId36" xr:uid="{EB15A9DD-30CE-4ADD-87F4-DA369E7C75C3}"/>
+    <hyperlink ref="A57" r:id="rId37" xr:uid="{A9583412-DC49-4F88-823E-93F35ABC3A80}"/>
+    <hyperlink ref="A58" r:id="rId38" xr:uid="{3E3E23B5-22B2-49A5-ABAE-67A3DDFEF724}"/>
+    <hyperlink ref="A59" r:id="rId39" xr:uid="{99FD36EE-1BBE-4504-ABF6-FF1BE94E1DA9}"/>
+    <hyperlink ref="A24" r:id="rId40" location="gid=1835304541" xr:uid="{C08A1F8D-5825-4569-BA16-C27FA1D8CDE4}"/>
+    <hyperlink ref="A56" r:id="rId41" location="gid=0" xr:uid="{F812F014-C2AA-4D90-AE24-BDE7837F4AFE}"/>
+    <hyperlink ref="A54" r:id="rId42" xr:uid="{9AE54292-5A62-484E-B413-CE6ED06B854A}"/>
+    <hyperlink ref="A5" r:id="rId43" xr:uid="{3A3AC866-FC89-482A-AAB2-AA129862ADA4}"/>
+    <hyperlink ref="A38" r:id="rId44" xr:uid="{76C8EB56-1656-44A4-8AF1-CAC1EC93B889}"/>
+    <hyperlink ref="A12" r:id="rId45" xr:uid="{DFB784F2-A2AE-4F97-B7B8-1E28010CCC17}"/>
+    <hyperlink ref="A60" r:id="rId46" xr:uid="{C15773D8-E2D2-4416-A71D-77E854DE7904}"/>
+    <hyperlink ref="A17" r:id="rId47" xr:uid="{4007B2F5-113E-4AD3-B8F8-B75E892D1F89}"/>
+    <hyperlink ref="A51" r:id="rId48" xr:uid="{0AF14E87-8BE6-41A8-B50D-119C5B2A12B5}"/>
+    <hyperlink ref="A10" r:id="rId49" xr:uid="{CC7B0D81-CDAA-4A20-8F3D-09E8DF18C0BF}"/>
+    <hyperlink ref="A61" r:id="rId50" xr:uid="{8AD3FE60-4361-4D93-A592-E973B624B54F}"/>
+    <hyperlink ref="A11" r:id="rId51" xr:uid="{3DB4D4C3-5932-42C3-A654-AB0A6C2365D1}"/>
+    <hyperlink ref="A49" r:id="rId52" xr:uid="{B8A0A5F5-194B-424D-B56C-6A7995344150}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2769DB-18AF-4BDD-8E16-0B68D85A4147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5148CA62-55B5-4179-9926-E351F8291B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="88">
   <si>
     <t>Reports Name</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Shrinkage</t>
+  </si>
+  <si>
+    <t>4/8/20206</t>
   </si>
 </sst>
 </file>
@@ -695,6 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -733,11 +737,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -772,11 +776,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -793,11 +797,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/06/2026</v>
+        <v>Updated as of 04/27/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -814,11 +818,11 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>46108</v>
+        <v>46140</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/27/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -835,11 +839,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46118</v>
+        <v>46140</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/06/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>74</v>
@@ -877,11 +881,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/06/2026</v>
+        <v>Updated as of 04/27/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -919,11 +923,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -941,11 +945,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -963,11 +967,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -985,11 +989,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1053,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1096,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1227,11 +1231,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46115</v>
+        <v>46140</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1263,11 +1267,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46115</v>
+        <v>46139</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 04/27/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1280,12 +1284,12 @@
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="2">
-        <v>46086</v>
+      <c r="C29" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 03/05/2026</v>
+        <v>Updated as of 4/8/20206</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>74</v>
@@ -1318,11 +1322,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1629,11 +1633,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1648,11 +1652,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1684,11 +1688,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1717,11 +1721,11 @@
         <v>57</v>
       </c>
       <c r="C54" s="2">
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/06/2026</v>
+        <v>Updated as of 04/27/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1735,11 +1739,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>Updated as of 04/06/2026</v>
+        <v>Updated as of 04/27/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1754,11 +1758,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1806,11 +1810,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1837,11 +1841,12 @@
         <v>83</v>
       </c>
       <c r="C61" s="2">
-        <v>46119</v>
+        <f ca="1">TODAY()</f>
+        <v>46140</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>Updated as of 04/07/2026</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>Updated as of 04/28/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5148CA62-55B5-4179-9926-E351F8291B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3D3D9E-6644-4371-A099-0ECF96DCBE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -797,11 +797,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/27/2026</v>
+        <v>Updated as of 05/05/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -818,11 +818,11 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/04/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -860,11 +860,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46115</v>
+        <v>46146</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 05/04/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -881,11 +881,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/27/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -923,11 +923,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -945,11 +945,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -967,11 +967,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -989,11 +989,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1053,11 +1053,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1096,11 +1096,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1231,11 +1231,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46140</v>
+        <v>46147</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/05/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1267,11 +1267,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/27/2026</v>
+        <v>Updated as of 05/04/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1303,11 +1303,11 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46115</v>
+        <v>46148</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1633,11 +1633,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1652,11 +1652,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1688,11 +1688,12 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <v>46140</v>
+        <f ca="1">TODAY()</f>
+        <v>46148</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1721,11 +1722,11 @@
         <v>57</v>
       </c>
       <c r="C54" s="2">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/27/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1739,11 +1740,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>Updated as of 04/27/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1758,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1810,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1842,11 +1843,11 @@
       </c>
       <c r="C61" s="2">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3D3D9E-6644-4371-A099-0ECF96DCBE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C263D-E950-4F84-BC7D-20DD431749B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -301,9 +301,6 @@
   </si>
   <si>
     <t>Shrinkage</t>
-  </si>
-  <si>
-    <t>4/8/20206</t>
   </si>
 </sst>
 </file>
@@ -737,11 +734,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -776,11 +773,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -797,11 +794,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/05/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -839,11 +836,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/28/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>74</v>
@@ -860,11 +857,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/04/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -902,11 +899,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46115</v>
+        <v>46160</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/03/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -923,11 +920,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -945,11 +942,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -967,11 +964,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -989,11 +986,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1053,11 +1050,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1095,12 +1092,11 @@
         <v>58</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" ref="C19" ca="1" si="3">TODAY()</f>
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 05/15/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1231,11 +1227,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/05/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1267,11 +1263,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/04/2026</v>
+        <v>Updated as of 05/06/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1284,12 +1280,12 @@
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>87</v>
+      <c r="C29" s="2">
+        <v>46149</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 4/8/20206</v>
+        <v>Updated as of 05/07/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>74</v>
@@ -1303,11 +1299,11 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/15/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1322,11 +1318,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1633,11 +1629,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1652,11 +1648,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1670,11 +1666,11 @@
         <v>55</v>
       </c>
       <c r="C51" s="2">
-        <v>46119</v>
+        <v>46160</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 04/07/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1689,11 +1685,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1722,11 +1718,11 @@
         <v>57</v>
       </c>
       <c r="C54" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" si="4">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" ref="D54:D59" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 05/15/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1736,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" si="3"/>
+        <v>Updated as of 05/15/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1755,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1780,7 +1776,7 @@
         <v>57</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1795,7 +1791,7 @@
         <v>57</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1811,11 +1807,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1827,7 +1823,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="5">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="4">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1843,11 +1839,11 @@
       </c>
       <c r="C61" s="2">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>Updated as of 05/06/2026</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C263D-E950-4F84-BC7D-20DD431749B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A019E0C8-DD08-4C9C-979C-D2CFA2FEA355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -734,11 +734,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -773,11 +773,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -794,11 +794,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/19/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -857,11 +857,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -878,11 +878,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/18/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -899,11 +899,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -942,11 +942,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -964,11 +964,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,12 +1049,12 @@
         <v>55</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17" ca="1" si="2">TODAY()</f>
-        <v>46160</v>
+        <f t="shared" ref="C17:C19" ca="1" si="2">TODAY()</f>
+        <v>46162</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1092,11 +1092,12 @@
         <v>58</v>
       </c>
       <c r="C19" s="2">
-        <v>46157</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46162</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 05/15/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1263,11 +1264,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/06/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1299,11 +1300,12 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46157</v>
+        <f ca="1">TODAY()</f>
+        <v>46162</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 05/15/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1318,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1629,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1648,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1666,11 +1668,12 @@
         <v>55</v>
       </c>
       <c r="C51" s="2">
-        <v>46160</v>
+        <f ca="1">TODAY()</f>
+        <v>46162</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1685,11 +1688,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1718,11 +1721,12 @@
         <v>57</v>
       </c>
       <c r="C54" s="2">
-        <v>46157</v>
+        <f ca="1">TODAY()</f>
+        <v>46162</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/15/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1736,11 +1740,11 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>Updated as of 05/15/2026</v>
+        <v>Updated as of 05/19/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1755,11 +1759,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1807,11 +1811,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1839,11 +1843,11 @@
       </c>
       <c r="C61" s="2">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/20/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A019E0C8-DD08-4C9C-979C-D2CFA2FEA355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2364C6F7-9B2A-40A8-8173-6784FE2A9958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -734,11 +734,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -773,11 +773,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -794,11 +794,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/19/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -857,11 +857,11 @@
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -878,11 +878,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -899,11 +899,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -920,11 +920,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -942,11 +942,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -964,11 +964,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1050,11 +1050,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17:C19" ca="1" si="2">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1228,11 +1228,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1669,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1740,11 +1740,12 @@
         <v>57</v>
       </c>
       <c r="C55" s="2">
-        <v>46161</v>
+        <f ca="1">TODAY()</f>
+        <v>46169</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>Updated as of 05/19/2026</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1759,11 +1760,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1811,11 +1812,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1843,11 +1844,11 @@
       </c>
       <c r="C61" s="2">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D61" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2364C6F7-9B2A-40A8-8173-6784FE2A9958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FCF21B-4A46-4DC6-A49A-1C74F633B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="88">
   <si>
     <t>Reports Name</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Shrinkage</t>
+  </si>
+  <si>
+    <t>5/29/20206</t>
   </si>
 </sst>
 </file>
@@ -733,12 +736,12 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2">
-        <v>46169</v>
+      <c r="C2" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 5/29/20206</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -771,13 +774,13 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="str">
         <f>C2</f>
-        <v>46169</v>
+        <v>5/29/20206</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 5/29/20206</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -794,11 +797,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/28/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -815,11 +818,11 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>46146</v>
+        <v>46164</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/04/2026</v>
+        <v>Updated as of 05/22/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -856,12 +859,12 @@
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="2">
-        <v>46169</v>
+      <c r="C8" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 5/29/20206</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -942,11 +945,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -964,11 +967,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -986,11 +989,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1050,11 +1053,11 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" ref="C17:C19" ca="1" si="2">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1093,11 +1096,11 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1264,11 +1267,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/20/2026</v>
+        <v>Updated as of 05/22/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1301,11 +1304,11 @@
       </c>
       <c r="C30" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1320,11 +1323,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1631,11 +1634,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1650,11 +1653,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1669,11 +1672,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1688,11 +1691,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1722,11 +1725,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1741,11 +1744,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1760,11 +1763,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1812,11 +1815,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 05/29/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1843,11 +1846,10 @@
         <v>83</v>
       </c>
       <c r="C61" s="2">
-        <f ca="1">TODAY()</f>
         <v>46169</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>Updated as of 05/27/2026</v>
       </c>
       <c r="E61" s="1" t="s">

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FCF21B-4A46-4DC6-A49A-1C74F633B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFC432D-123D-44CA-87F5-3A894527F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -301,9 +301,6 @@
   </si>
   <si>
     <t>Shrinkage</t>
-  </si>
-  <si>
-    <t>5/29/20206</t>
   </si>
 </sst>
 </file>
@@ -736,12 +733,12 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>87</v>
+      <c r="C2" s="2">
+        <v>46177</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 5/29/20206</v>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -774,13 +771,13 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="str">
+      <c r="C4" s="2">
         <f>C2</f>
-        <v>5/29/20206</v>
+        <v>46177</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 5/29/20206</v>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -797,11 +794,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46170</v>
+        <v>46177</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/28/2026</v>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -818,11 +815,11 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/22/2026</v>
+        <v>Updated as of 06/02/2026</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -859,12 +856,12 @@
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>87</v>
+      <c r="C8" s="2">
+        <v>46175</v>
       </c>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 5/29/20206</v>
+        <v>Updated as of 06/02/2026</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -881,11 +878,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 06/01/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -902,11 +899,11 @@
         <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>46169</v>
+        <v>46178</v>
       </c>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -923,11 +920,11 @@
         <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>46169</v>
+        <v>46178</v>
       </c>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -945,11 +942,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -967,11 +964,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -989,11 +986,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1052,12 +1049,11 @@
         <v>55</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:C19" ca="1" si="2">TODAY()</f>
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1095,12 +1091,11 @@
         <v>58</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" ca="1" si="2"/>
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 06/03/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1231,11 +1226,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/27/2026</v>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1267,11 +1262,11 @@
         <v>50</v>
       </c>
       <c r="C28" s="2">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/22/2026</v>
+        <v>Updated as of 06/03/2026</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
@@ -1285,11 +1280,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>46149</v>
+        <v>46177</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/07/2026</v>
+        <v>Updated as of 06/04/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>74</v>
@@ -1303,12 +1298,11 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 06/02/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1323,11 +1317,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1634,11 +1628,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1653,11 +1647,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1672,11 +1666,11 @@
       </c>
       <c r="C51" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D51" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1691,11 +1685,11 @@
       </c>
       <c r="C52" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D52" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 05/29/2026</v>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1725,11 +1719,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="3">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" ref="D54:D59" ca="1" si="2">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1744,11 +1738,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1763,11 +1757,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1784,7 +1778,7 @@
         <v>57</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
@@ -1799,7 +1793,7 @@
         <v>57</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
@@ -1815,11 +1809,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>Updated as of 05/29/2026</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
@@ -1831,7 +1825,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="4">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="3">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
@@ -1846,11 +1840,11 @@
         <v>83</v>
       </c>
       <c r="C61" s="2">
-        <v>46169</v>
+        <v>46178</v>
       </c>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>Updated as of 05/27/2026</v>
+        <f t="shared" si="3"/>
+        <v>Updated as of 06/05/2026</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFC432D-123D-44CA-87F5-3A894527F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C553BEEE-6375-4B06-A422-C52F937FDBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -734,11 +734,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -773,11 +773,11 @@
       </c>
       <c r="C4" s="2">
         <f>C2</f>
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -794,11 +794,11 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -878,11 +878,11 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/01/2026</v>
+        <v>Updated as of 06/08/2026</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -942,11 +942,11 @@
       </c>
       <c r="C12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -964,11 +964,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -1049,11 +1049,11 @@
         <v>55</v>
       </c>
       <c r="C17" s="2">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1091,11 +1091,11 @@
         <v>58</v>
       </c>
       <c r="C19" s="2">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/03/2026</v>
+        <v>Updated as of 06/08/2026</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1226,11 +1226,11 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/08/2026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
@@ -1280,11 +1280,11 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/04/2026</v>
+        <v>Updated as of 06/08/2026</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>74</v>
@@ -1298,11 +1298,11 @@
         <v>84</v>
       </c>
       <c r="C30" s="2">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/02/2026</v>
+        <v>Updated as of 06/08/2026</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="C31" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D31" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="C49" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="C50" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D50" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
@@ -1665,12 +1665,11 @@
         <v>55</v>
       </c>
       <c r="C51" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
@@ -1684,12 +1683,11 @@
         <v>3</v>
       </c>
       <c r="C52" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <f t="shared" si="0"/>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
@@ -1719,11 +1717,11 @@
       </c>
       <c r="C54" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" ref="D54:D59" ca="1" si="2">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -1738,11 +1736,11 @@
       </c>
       <c r="C55" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D55" s="1" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
@@ -1757,11 +1755,11 @@
       </c>
       <c r="C56" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D56" s="1" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -1809,11 +1807,11 @@
       </c>
       <c r="C59" s="2">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="D59" s="1" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/05/2026</v>
+        <v>Updated as of 06/09/2026</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>

--- a/Files/Reports Update.xlsx
+++ b/Files/Reports Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\pnmac.com\profiles\Users\v-ldemesa.V2\Desktop\WFM Site\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C553BEEE-6375-4B06-A422-C52F937FDBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B658AD-F11B-48BD-8B3F-F6932054789F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A15541CF-20B7-46A3-8A04-360D148BB048}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="87">
   <si>
     <t>Reports Name</t>
   </si>
@@ -697,16 +697,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E5AA26-CA30-44A4-902F-617B1FABB1FF}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="27.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16383" width="9.140625" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="27.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.26953125" style="1" customWidth="1"/>
+    <col min="5" max="16383" width="9.1796875" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -726,19 +726,17 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2">
-        <v>46182</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="1" t="str">
         <f t="shared" ref="D2:D53" si="0">IF(OR(C2="-",C2=""),"",$C$1&amp;" "&amp;TEXT(C2,"mm/dd/yyyy"))</f>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E2" s="1" t="s">
         <v>74</v>
@@ -747,7 +745,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="str">
@@ -764,20 +762,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2">
-        <f>C2</f>
-        <v>46182</v>
-      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E4" s="1" t="s">
         <v>74</v>
@@ -786,19 +781,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2">
-        <v>46182</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E5" s="1" t="s">
         <v>74</v>
@@ -807,19 +800,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
-        <v>46175</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/02/2026</v>
+        <v/>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -828,19 +819,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="2">
-        <v>46160</v>
-      </c>
+      <c r="C7" s="2"/>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 05/18/2026</v>
+        <v/>
       </c>
       <c r="E7" s="1" t="s">
         <v>74</v>
@@ -849,19 +838,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="2">
-        <v>46175</v>
-      </c>
+      <c r="C8" s="2"/>
       <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/02/2026</v>
+        <v/>
       </c>
       <c r="E8" s="1" t="s">
         <v>74</v>
@@ -870,19 +857,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2">
-        <v>46181</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/08/2026</v>
+        <v/>
       </c>
       <c r="E9" s="1" t="s">
         <v>74</v>
@@ -891,19 +876,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="2">
-        <v>46178</v>
-      </c>
+      <c r="C10" s="2"/>
       <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v/>
       </c>
       <c r="E10" s="1" t="s">
         <v>74</v>
@@ -912,19 +895,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2">
-        <v>46178</v>
-      </c>
+      <c r="C11" s="2"/>
       <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/05/2026</v>
+        <v/>
       </c>
       <c r="E11" s="1" t="s">
         <v>74</v>
@@ -933,20 +914,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C12" s="2"/>
       <c r="D12" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E12" s="1" t="s">
         <v>74</v>
@@ -955,20 +933,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="2">
-        <f t="shared" ref="C13:C14" ca="1" si="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C13" s="2"/>
       <c r="D13" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E13" s="1" t="s">
         <v>74</v>
@@ -977,20 +952,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="2">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
-      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E14" s="1" t="s">
         <v>74</v>
@@ -999,16 +971,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1020,16 +990,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C16" s="2"/>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1041,19 +1009,17 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="2">
-        <v>46182</v>
-      </c>
+      <c r="C17" s="2"/>
       <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1062,16 +1028,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C18" s="2"/>
       <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1083,19 +1047,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>79</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="2">
-        <v>46181</v>
-      </c>
+      <c r="C19" s="2"/>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/08/2026</v>
+        <v/>
       </c>
       <c r="E19" s="1" t="s">
         <v>74</v>
@@ -1104,16 +1066,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C20" s="2"/>
       <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1125,16 +1085,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C21" s="2"/>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1146,16 +1104,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C22" s="2"/>
       <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1164,16 +1120,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1182,16 +1136,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C24" s="2"/>
       <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1200,16 +1152,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1218,34 +1168,30 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="2">
-        <v>46181</v>
-      </c>
+      <c r="C26" s="2"/>
       <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/08/2026</v>
+        <v/>
       </c>
       <c r="E26" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1254,89 +1200,78 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="2">
-        <v>46176</v>
-      </c>
+      <c r="C28" s="2"/>
       <c r="D28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/03/2026</v>
+        <v/>
       </c>
       <c r="E28" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="2">
-        <v>46181</v>
-      </c>
+      <c r="C29" s="2"/>
       <c r="D29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/08/2026</v>
+        <v/>
       </c>
       <c r="E29" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="2">
-        <v>46181</v>
-      </c>
+      <c r="C30" s="2"/>
       <c r="D30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/08/2026</v>
+        <v/>
       </c>
       <c r="E30" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C31" s="2"/>
       <c r="D31" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E31" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1345,16 +1280,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1363,16 +1296,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C34" s="2"/>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1381,16 +1312,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C35" s="2"/>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1399,16 +1328,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C36" s="2"/>
       <c r="D36" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1417,7 +1344,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>48</v>
       </c>
@@ -1433,7 +1360,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>37</v>
       </c>
@@ -1449,7 +1376,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>38</v>
       </c>
@@ -1465,7 +1392,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>39</v>
       </c>
@@ -1481,16 +1408,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C41" s="2"/>
       <c r="D41" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1499,16 +1424,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1517,16 +1440,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1535,16 +1456,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1553,7 +1472,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>44</v>
       </c>
@@ -1569,7 +1488,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>45</v>
       </c>
@@ -1585,7 +1504,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>80</v>
       </c>
@@ -1601,16 +1520,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C48" s="2"/>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1619,87 +1536,75 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C49" s="2"/>
       <c r="D49" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E49" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C50" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C50" s="2"/>
       <c r="D50" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="E50" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>63</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="2">
-        <v>46182</v>
-      </c>
+      <c r="C51" s="2"/>
       <c r="D51" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E51" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="2">
-        <v>46182</v>
-      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Updated as of 06/09/2026</v>
+        <v/>
       </c>
       <c r="E52" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C53" s="2"/>
       <c r="D53" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1708,82 +1613,71 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C54" s="2"/>
       <c r="D54" s="1" t="str">
-        <f t="shared" ref="D54:D59" ca="1" si="2">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" ref="D54:D59" si="1">IF(OR(C54="-",C54=""),"",$C$1&amp;" "&amp;TEXT(C54,"mm/dd/yyyy"))</f>
+        <v/>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C55" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C55" s="2"/>
       <c r="D55" s="1" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="E55" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C56" s="2"/>
       <c r="D56" s="1" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="C57" s="2"/>
       <c r="D57" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E57" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>70</v>
       </c>
@@ -1791,58 +1685,53 @@
         <v>57</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E58" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46182</v>
-      </c>
+      <c r="C59" s="2"/>
       <c r="D59" s="1" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Updated as of 06/09/2026</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="E59" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="1" t="str">
-        <f t="shared" ref="D60:D61" si="3">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
+        <f t="shared" ref="D60:D61" si="2">IF(OR(C60="-",C60=""),"",$C$1&amp;" "&amp;TEXT(C60,"mm/dd/yyyy"))</f>
         <v/>
       </c>
       <c r="E60" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="2">
-        <v>46178</v>
-      </c>
+      <c r="C61" s="2"/>
       <c r="D61" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>Updated as of 06/05/2026</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="E61" s="1" t="s">
         <v>74</v>
